--- a/Versão5/SIS/Ontologia_Luminotecnica.xlsx
+++ b/Versão5/SIS/Ontologia_Luminotecnica.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ILUM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BE782C-F0AF-40EB-A009-B3EC98685FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F696E18-9EC2-4764-8DFC-26848F5D3F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -2063,14 +2063,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="33.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.69140625" customWidth="1"/>
+    <col min="2" max="2" width="33.69140625" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>46</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>48</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>50</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="38" t="s">
         <v>56</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
@@ -2259,19 +2259,19 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46244.669257175927</v>
+        <v>46249.427708680552</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>69</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>72</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>73</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>74</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>90</v>
       </c>
@@ -2347,35 +2347,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA30"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="59" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="64" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8" style="59" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.5703125" style="59" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="59" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" style="59" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="40.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.42578125" style="59" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="23.85546875" style="65" customWidth="1"/>
-    <col min="26" max="26" width="7.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="67.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="59"/>
+    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" style="59" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.15234375" style="59" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.69140625" style="64" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.4609375" style="59" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.23046875" style="59" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.921875" style="59" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" style="59" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.4609375" style="59" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.921875" style="59" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10" style="59" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.84375" style="65" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.07421875" style="59" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.921875" style="59" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="44" t="s">
         <v>156</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="56">
         <v>2</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>Electrical Lighting System</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="56">
         <v>3</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>Electrical Lighting System</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="56">
         <v>4</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="56">
         <v>5</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="56">
         <v>6</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="56">
         <v>7</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="56">
         <v>8</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="56">
         <v>9</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="56">
         <v>10</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="56">
         <v>11</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="56">
         <v>12</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="56">
         <v>13</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="56">
         <v>14</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="56">
         <v>15</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="56">
         <v>16</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="56">
         <v>17</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="56">
         <v>18</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="56">
         <v>19</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="56">
         <v>20</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="56">
         <v>21</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="56">
         <v>22</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="56">
         <v>23</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="56">
         <v>24</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="56">
         <v>25</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="56">
         <v>26</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="56">
         <v>27</v>
       </c>
@@ -4752,7 +4752,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="56">
         <v>28</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="56">
         <v>29</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="56">
         <v>30</v>
       </c>
@@ -5064,6 +5064,9 @@
     <cfRule type="duplicateValues" dxfId="7" priority="42"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -5071,15 +5074,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -5144,7 +5147,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5209,7 +5212,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -5292,30 +5295,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="64.85546875" customWidth="1"/>
-    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" customWidth="1"/>
-    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.28515625" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.7109375" customWidth="1"/>
-    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64.84375" customWidth="1"/>
+    <col min="8" max="8" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.53515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.3828125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.3046875" customWidth="1"/>
+    <col min="14" max="14" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.3046875" customWidth="1"/>
+    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.69140625" customWidth="1"/>
+    <col min="18" max="18" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -5374,7 +5377,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -5433,7 +5436,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="21">
         <v>3</v>
       </c>
@@ -5492,7 +5495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21">
         <v>4</v>
       </c>
@@ -5551,7 +5554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="21">
         <v>5</v>
       </c>
@@ -5610,7 +5613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="21">
         <v>6</v>
       </c>
@@ -5669,7 +5672,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="21">
         <v>7</v>
       </c>
@@ -5728,7 +5731,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="21">
         <v>8</v>
       </c>
@@ -5787,7 +5790,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="21">
         <v>9</v>
       </c>
@@ -5846,7 +5849,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="21">
         <v>10</v>
       </c>
@@ -5905,7 +5908,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="21">
         <v>11</v>
       </c>
@@ -5964,7 +5967,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="21">
         <v>12</v>
       </c>
@@ -6023,7 +6026,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="21">
         <v>13</v>
       </c>
@@ -6082,7 +6085,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="21">
         <v>14</v>
       </c>
@@ -6151,15 +6154,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="27" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="27" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -6182,7 +6185,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>

--- a/Versão5/SIS/Ontologia_Luminotecnica.xlsx
+++ b/Versão5/SIS/Ontologia_Luminotecnica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F696E18-9EC2-4764-8DFC-26848F5D3F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718E354B-CF9E-48B6-9FFD-18E09C94FC8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="278">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -327,12 +327,6 @@
     <t>é.dentro.de</t>
   </si>
   <si>
-    <t>CategoriaRvt</t>
-  </si>
-  <si>
-    <t>ClasseIfc</t>
-  </si>
-  <si>
     <t>ABNT</t>
   </si>
   <si>
@@ -894,6 +888,24 @@
   </si>
   <si>
     <t>"[ OST_LightingDevices ]"</t>
+  </si>
+  <si>
+    <t>Electrical Lighting System</t>
+  </si>
+  <si>
+    <t>Classe IFC</t>
+  </si>
+  <si>
+    <t>Atributo IFC</t>
+  </si>
+  <si>
+    <t>[ - ]</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Categoria Rvt</t>
   </si>
 </sst>
 </file>
@@ -2078,7 +2090,7 @@
         <v>47</v>
       </c>
       <c r="C1" s="40" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2089,7 +2101,7 @@
         <v>49</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2097,10 +2109,10 @@
         <v>50</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C3" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2111,7 +2123,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2123,7 +2135,7 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2135,7 +2147,7 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2146,7 +2158,7 @@
         <v>55</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2154,10 +2166,10 @@
         <v>56</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2168,7 +2180,7 @@
         <v>58</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2179,7 +2191,7 @@
         <v>60</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2190,7 +2202,7 @@
         <v>60</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2201,7 +2213,7 @@
         <v>60</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2212,7 +2224,7 @@
         <v>60</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2223,7 +2235,7 @@
         <v>60</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2234,7 +2246,7 @@
         <v>60</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2245,7 +2257,7 @@
         <v>60</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2253,10 +2265,10 @@
         <v>67</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2265,10 +2277,10 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46249.427708680552</v>
+        <v>46253.808837384262</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2279,7 +2291,7 @@
         <v>70</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2290,7 +2302,7 @@
         <v>60</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2301,7 +2313,7 @@
         <v>60</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2309,10 +2321,10 @@
         <v>73</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2320,22 +2332,22 @@
         <v>74</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B24" s="17" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific objects of Lighting</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2346,7 +2358,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA30"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
@@ -2362,22 +2374,24 @@
     <col min="15" max="15" width="9.69140625" style="59" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="28.69140625" style="59" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="28.921875" style="59" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.69140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6" style="59" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.3828125" style="59" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.4609375" style="59" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.921875" style="59" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.69140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10" style="59" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.84375" style="65" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.07421875" style="59" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.921875" style="59" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.15234375" style="59"/>
+    <col min="18" max="18" width="13.921875" style="59" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6" style="59" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.921875" style="59" customWidth="1"/>
+    <col min="23" max="23" width="4.921875" style="59" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10" style="59" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.765625" style="59" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.84375" style="65" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6" style="59" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.07421875" style="59" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="44" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B1" s="45" t="s">
         <v>42</v>
@@ -2410,7 +2424,7 @@
         <v>4</v>
       </c>
       <c r="L1" s="36" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M1" s="36" t="s">
         <v>5</v>
@@ -2427,55 +2441,61 @@
       <c r="Q1" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="R1" s="36" t="s">
-        <v>158</v>
+      <c r="R1" s="37" t="s">
+        <v>86</v>
       </c>
       <c r="S1" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="T1" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="36" t="s">
+      <c r="U1" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="U1" s="47" t="s">
+      <c r="V1" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="36" t="s">
+      <c r="W1" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="60" t="s">
+      <c r="X1" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="36" t="s">
+      <c r="Y1" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z1" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="AA1" s="36" t="s">
+        <v>273</v>
+      </c>
+      <c r="AB1" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="AC1" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="Y1" s="36" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z1" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA1" s="37" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="56">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G2" s="57" t="s">
         <v>9</v>
@@ -2509,64 +2529,69 @@
         <v>Circuito.Luz.Geral</v>
       </c>
       <c r="P2" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q2" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="R2" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="S2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="U2" s="30" t="str">
+        <f t="shared" ref="U2:U3" si="4">SUBSTITUTE(D2, "_", " ")</f>
+        <v>Sistemas.Elétricos</v>
+      </c>
+      <c r="V2" s="30" t="str">
+        <f t="shared" ref="V2:V3" si="5">SUBSTITUTE(E2, "_", " ")</f>
+        <v>Sistemas.de.Iluminação</v>
+      </c>
+      <c r="W2" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X2" s="58" t="str">
+        <f t="shared" ref="X2:X30" si="6">CONCATENATE("Key-ILUM-",A2)</f>
+        <v>Key-ILUM-2</v>
+      </c>
+      <c r="Y2" s="61" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z2" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AA2" s="61" t="s">
         <v>209</v>
       </c>
-      <c r="Q2" s="53" t="s">
-        <v>208</v>
-      </c>
-      <c r="R2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="T2" s="30" t="str">
-        <f t="shared" ref="T2:T3" si="4">SUBSTITUTE(D2, "_", " ")</f>
-        <v>Sistemas.Elétricos</v>
-      </c>
-      <c r="U2" s="30" t="str">
-        <f t="shared" ref="U2:U3" si="5">SUBSTITUTE(E2, "_", " ")</f>
-        <v>Sistemas.de.Iluminação</v>
-      </c>
-      <c r="V2" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W2" s="58" t="str">
-        <f t="shared" ref="W2:W30" si="6">CONCATENATE("Key-ILUM-",A2)</f>
-        <v>Key-ILUM-2</v>
-      </c>
-      <c r="X2" s="61" t="s">
-        <v>210</v>
-      </c>
-      <c r="Y2" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="Z2" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="AA2" s="30" t="str">
-        <f t="shared" ref="AA2:AA3" si="7">_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Electrical Lighting System</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB2" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC2" s="30" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="56">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E3" s="43" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F3" s="43" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G3" s="57" t="s">
         <v>9</v>
@@ -2600,64 +2625,69 @@
         <v>Circuito.Luz.Emergência</v>
       </c>
       <c r="P3" s="53" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Q3" s="53" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="R3" s="30" t="s">
-        <v>9</v>
+        <v>272</v>
       </c>
       <c r="S3" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="T3" s="30" t="str">
+        <v>9</v>
+      </c>
+      <c r="T3" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="U3" s="30" t="str">
         <f t="shared" si="4"/>
         <v>Sistemas.Elétricos</v>
       </c>
-      <c r="U3" s="30" t="str">
+      <c r="V3" s="30" t="str">
         <f t="shared" si="5"/>
         <v>Sistemas.de.Iluminação</v>
       </c>
-      <c r="V3" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W3" s="58" t="str">
+      <c r="W3" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X3" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-3</v>
       </c>
-      <c r="X3" s="61" t="s">
-        <v>210</v>
-      </c>
       <c r="Y3" s="61" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Z3" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="AA3" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Electrical Lighting System</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA3" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB3" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC3" s="30" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="56">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E4" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F4" s="62" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G4" s="63" t="s">
         <v>9</v>
@@ -2687,65 +2717,71 @@
         <v>Luminária</v>
       </c>
       <c r="O4" s="30" t="str">
-        <f t="shared" ref="O4:O30" si="8">IF(ISNUMBER(FIND("Ifc",F4)),CONCATENATE("Classe IFC:   ",F4),CONCATENATE("",F4))</f>
+        <f t="shared" ref="O4:O30" si="7">IF(ISNUMBER(FIND("Ifc",F4)),CONCATENATE("Classe IFC:   ",F4),CONCATENATE("",F4))</f>
         <v>Luz.Aletas</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q4" s="30" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="R4" s="30" t="s">
-        <v>9</v>
+        <v>157</v>
       </c>
       <c r="S4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T4" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U4" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V4" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W4" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W4" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X4" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-4</v>
       </c>
-      <c r="X4" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y4" s="61" t="s">
-        <v>266</v>
+      <c r="Y4" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z4" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA4" s="30" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA4" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB4" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC4" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="56">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E5" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F5" s="62" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G5" s="63" t="s">
         <v>9</v>
@@ -2775,65 +2811,71 @@
         <v>Luminária</v>
       </c>
       <c r="O5" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">Luz.Antiofuscamento </v>
       </c>
       <c r="P5" s="30" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q5" s="30" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="R5" s="30" t="s">
-        <v>9</v>
+        <v>158</v>
       </c>
       <c r="S5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T5" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T5" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U5" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V5" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W5" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W5" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X5" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-5</v>
       </c>
-      <c r="X5" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y5" s="61" t="s">
-        <v>266</v>
+      <c r="Y5" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z5" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA5" s="30" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA5" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB5" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC5" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="56">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E6" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F6" s="62" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G6" s="63" t="s">
         <v>9</v>
@@ -2863,65 +2905,71 @@
         <v>Luminária</v>
       </c>
       <c r="O6" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Arandela</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="Q6" s="30" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R6" s="30" t="s">
-        <v>9</v>
+        <v>159</v>
       </c>
       <c r="S6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T6" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T6" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U6" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V6" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W6" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W6" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X6" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-6</v>
       </c>
-      <c r="X6" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y6" s="61" t="s">
-        <v>266</v>
+      <c r="Y6" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z6" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA6" s="30" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA6" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB6" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC6" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="56">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E7" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F7" s="62" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G7" s="63" t="s">
         <v>9</v>
@@ -2951,65 +2999,71 @@
         <v>Luminária</v>
       </c>
       <c r="O7" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Baliza</v>
       </c>
       <c r="P7" s="30" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q7" s="30" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R7" s="30" t="s">
-        <v>9</v>
+        <v>160</v>
       </c>
       <c r="S7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T7" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T7" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U7" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V7" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W7" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W7" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X7" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-7</v>
       </c>
-      <c r="X7" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y7" s="61" t="s">
-        <v>266</v>
+      <c r="Y7" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z7" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA7" s="30" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA7" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB7" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC7" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="56">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E8" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F8" s="62" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G8" s="63" t="s">
         <v>9</v>
@@ -3039,65 +3093,71 @@
         <v>Luminária</v>
       </c>
       <c r="O8" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Difusa</v>
       </c>
       <c r="P8" s="30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R8" s="30" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="S8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T8" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U8" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V8" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W8" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W8" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X8" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-8</v>
       </c>
-      <c r="X8" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y8" s="61" t="s">
-        <v>266</v>
+      <c r="Y8" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z8" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA8" s="30" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA8" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB8" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC8" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="56">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E9" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F9" s="62" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G9" s="63" t="s">
         <v>9</v>
@@ -3127,65 +3187,71 @@
         <v>Luminária</v>
       </c>
       <c r="O9" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Embutida.Fixa</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>9</v>
+        <v>162</v>
       </c>
       <c r="S9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T9" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T9" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U9" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V9" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W9" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W9" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X9" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-9</v>
       </c>
-      <c r="X9" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y9" s="61" t="s">
-        <v>266</v>
+      <c r="Y9" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z9" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA9" s="30" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA9" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB9" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC9" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="56">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E10" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F10" s="62" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G10" s="63" t="s">
         <v>9</v>
@@ -3215,65 +3281,71 @@
         <v>Luminária</v>
       </c>
       <c r="O10" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Embutida.Orientável</v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Q10" s="30" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="R10" s="30" t="s">
-        <v>9</v>
+        <v>163</v>
       </c>
       <c r="S10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T10" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U10" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V10" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W10" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W10" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X10" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-10</v>
       </c>
-      <c r="X10" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y10" s="61" t="s">
-        <v>266</v>
+      <c r="Y10" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z10" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA10" s="30" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA10" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB10" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC10" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="56">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E11" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F11" s="62" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G11" s="63" t="s">
         <v>9</v>
@@ -3291,77 +3363,83 @@
         <v>9</v>
       </c>
       <c r="L11" s="34" t="str">
-        <f t="shared" ref="L11" si="9">CONCATENATE("", C11)</f>
+        <f t="shared" ref="L11" si="8">CONCATENATE("", C11)</f>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M11" s="34" t="str">
-        <f t="shared" ref="M11" si="10">CONCATENATE("", D11)</f>
+        <f t="shared" ref="M11" si="9">CONCATENATE("", D11)</f>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N11" s="34" t="str">
-        <f t="shared" ref="N11" si="11">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N11" si="10">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
         <v>Luminária</v>
       </c>
       <c r="O11" s="30" t="str">
-        <f t="shared" ref="O11" si="12">IF(ISNUMBER(FIND("Ifc",F11)),CONCATENATE("Classe IFC:   ",F11),CONCATENATE("",F11))</f>
+        <f t="shared" ref="O11" si="11">IF(ISNUMBER(FIND("Ifc",F11)),CONCATENATE("Classe IFC:   ",F11),CONCATENATE("",F11))</f>
         <v>Luz.Externa</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Q11" s="30" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R11" s="30" t="s">
-        <v>9</v>
+        <v>251</v>
       </c>
       <c r="S11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T11" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U11" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V11" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W11" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W11" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X11" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-11</v>
       </c>
-      <c r="X11" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y11" s="61" t="s">
-        <v>266</v>
+      <c r="Y11" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z11" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA11" s="30" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA11" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB11" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC11" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="56">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E12" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F12" s="62" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G12" s="63" t="s">
         <v>9</v>
@@ -3391,65 +3469,71 @@
         <v>Luminária</v>
       </c>
       <c r="O12" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Externa.Urbana</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Q12" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="R12" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="R12" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="S12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T12" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T12" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U12" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V12" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W12" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W12" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X12" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-12</v>
       </c>
-      <c r="X12" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y12" s="61" t="s">
-        <v>266</v>
+      <c r="Y12" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z12" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA12" s="30" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA12" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB12" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC12" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="56">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E13" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F13" s="62" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G13" s="63" t="s">
         <v>9</v>
@@ -3479,65 +3563,71 @@
         <v>Luminária</v>
       </c>
       <c r="O13" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Feixe.Amplo</v>
       </c>
       <c r="P13" s="30" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="Q13" s="30" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="R13" s="30" t="s">
-        <v>9</v>
+        <v>175</v>
       </c>
       <c r="S13" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T13" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T13" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U13" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V13" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W13" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W13" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X13" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-13</v>
       </c>
-      <c r="X13" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y13" s="61" t="s">
-        <v>266</v>
+      <c r="Y13" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z13" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA13" s="30" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA13" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB13" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC13" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="56">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E14" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F14" s="62" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G14" s="63" t="s">
         <v>9</v>
@@ -3567,65 +3657,71 @@
         <v>Luminária</v>
       </c>
       <c r="O14" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Gôndola</v>
       </c>
       <c r="P14" s="30" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="Q14" s="30" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R14" s="30" t="s">
-        <v>9</v>
+        <v>164</v>
       </c>
       <c r="S14" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T14" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T14" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U14" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V14" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W14" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W14" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X14" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-14</v>
       </c>
-      <c r="X14" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y14" s="61" t="s">
-        <v>266</v>
+      <c r="Y14" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z14" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA14" s="30" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA14" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB14" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC14" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="56">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E15" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F15" s="62" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G15" s="63" t="s">
         <v>9</v>
@@ -3655,65 +3751,71 @@
         <v>Luminária</v>
       </c>
       <c r="O15" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Grande.Altura</v>
       </c>
       <c r="P15" s="30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Q15" s="30" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R15" s="30" t="s">
-        <v>9</v>
+        <v>165</v>
       </c>
       <c r="S15" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T15" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T15" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U15" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V15" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W15" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W15" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X15" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-15</v>
       </c>
-      <c r="X15" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y15" s="61" t="s">
-        <v>266</v>
+      <c r="Y15" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z15" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA15" s="30" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA15" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB15" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC15" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="56">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E16" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F16" s="62" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G16" s="63" t="s">
         <v>9</v>
@@ -3743,65 +3845,71 @@
         <v>Luminária</v>
       </c>
       <c r="O16" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Hermética</v>
       </c>
       <c r="P16" s="30" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q16" s="30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="R16" s="30" t="s">
-        <v>9</v>
+        <v>166</v>
       </c>
       <c r="S16" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T16" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T16" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U16" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V16" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W16" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W16" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X16" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-16</v>
       </c>
-      <c r="X16" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y16" s="61" t="s">
-        <v>266</v>
+      <c r="Y16" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z16" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA16" s="30" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA16" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB16" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC16" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="56">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E17" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F17" s="62" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G17" s="63" t="s">
         <v>9</v>
@@ -3831,65 +3939,71 @@
         <v>Luminária</v>
       </c>
       <c r="O17" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.LEDFita</v>
       </c>
       <c r="P17" s="30" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q17" s="30" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="R17" s="30" t="s">
-        <v>9</v>
+        <v>167</v>
       </c>
       <c r="S17" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T17" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T17" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U17" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V17" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W17" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W17" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X17" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-17</v>
       </c>
-      <c r="X17" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y17" s="61" t="s">
-        <v>267</v>
+      <c r="Y17" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z17" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA17" s="30" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA17" s="61" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB17" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC17" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="56">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E18" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F18" s="62" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G18" s="63" t="s">
         <v>9</v>
@@ -3919,153 +4033,165 @@
         <v>Luminária</v>
       </c>
       <c r="O18" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.LEDTubular</v>
       </c>
       <c r="P18" s="30" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q18" s="30" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="R18" s="30" t="s">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="S18" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T18" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T18" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U18" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V18" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W18" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W18" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X18" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-18</v>
       </c>
-      <c r="X18" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y18" s="61" t="s">
-        <v>267</v>
+      <c r="Y18" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z18" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA18" s="30" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA18" s="61" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB18" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC18" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="56">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E19" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F19" s="62" t="s">
+        <v>241</v>
+      </c>
+      <c r="G19" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L19" s="34" t="str">
+        <f t="shared" ref="L19" si="12">CONCATENATE("", C19)</f>
+        <v>LuminoTécnicos</v>
+      </c>
+      <c r="M19" s="34" t="str">
+        <f t="shared" ref="M19" si="13">CONCATENATE("", D19)</f>
+        <v>Elemento.Iluminação</v>
+      </c>
+      <c r="N19" s="34" t="str">
+        <f t="shared" ref="N19" si="14">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E19),"."," ")," De "," de "))</f>
+        <v>Luminária</v>
+      </c>
+      <c r="O19" s="30" t="str">
+        <f t="shared" ref="O19" si="15">IF(ISNUMBER(FIND("Ifc",F19)),CONCATENATE("Classe IFC:   ",F19),CONCATENATE("",F19))</f>
+        <v>Luz.TuboFluorescente</v>
+      </c>
+      <c r="P19" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q19" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="G19" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="K19" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="L19" s="34" t="str">
-        <f t="shared" ref="L19" si="13">CONCATENATE("", C19)</f>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M19" s="34" t="str">
-        <f t="shared" ref="M19" si="14">CONCATENATE("", D19)</f>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N19" s="34" t="str">
-        <f t="shared" ref="N19" si="15">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E19),"."," ")," De "," de "))</f>
-        <v>Luminária</v>
-      </c>
-      <c r="O19" s="30" t="str">
-        <f t="shared" ref="O19" si="16">IF(ISNUMBER(FIND("Ifc",F19)),CONCATENATE("Classe IFC:   ",F19),CONCATENATE("",F19))</f>
-        <v>Luz.TuboFluorescente</v>
-      </c>
-      <c r="P19" s="30" t="s">
+      <c r="R19" s="30" t="s">
         <v>244</v>
       </c>
-      <c r="Q19" s="30" t="s">
-        <v>245</v>
-      </c>
-      <c r="R19" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="S19" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T19" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T19" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U19" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V19" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W19" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W19" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X19" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-19</v>
       </c>
-      <c r="X19" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y19" s="61" t="s">
-        <v>266</v>
+      <c r="Y19" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z19" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA19" s="30" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA19" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB19" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC19" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="56">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E20" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F20" s="62" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G20" s="63" t="s">
         <v>9</v>
@@ -4095,65 +4221,71 @@
         <v>Luminária</v>
       </c>
       <c r="O20" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Linear</v>
       </c>
       <c r="P20" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q20" s="30" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R20" s="30" t="s">
-        <v>9</v>
+        <v>169</v>
       </c>
       <c r="S20" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T20" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T20" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U20" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V20" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W20" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W20" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X20" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-20</v>
       </c>
-      <c r="X20" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y20" s="61" t="s">
-        <v>266</v>
+      <c r="Y20" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z20" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA20" s="30" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA20" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB20" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC20" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="56">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E21" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F21" s="62" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G21" s="63" t="s">
         <v>9</v>
@@ -4183,65 +4315,71 @@
         <v>Luminária</v>
       </c>
       <c r="O21" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Painel</v>
       </c>
       <c r="P21" s="30" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Q21" s="30" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="R21" s="30" t="s">
-        <v>9</v>
+        <v>170</v>
       </c>
       <c r="S21" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T21" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T21" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U21" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V21" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W21" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W21" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X21" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-21</v>
       </c>
-      <c r="X21" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y21" s="61" t="s">
-        <v>266</v>
+      <c r="Y21" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z21" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA21" s="30" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA21" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB21" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC21" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="56">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E22" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F22" s="62" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G22" s="63" t="s">
         <v>9</v>
@@ -4271,65 +4409,71 @@
         <v>Luminária</v>
       </c>
       <c r="O22" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Pendente</v>
       </c>
       <c r="P22" s="30" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Q22" s="30" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R22" s="30" t="s">
-        <v>9</v>
+        <v>176</v>
       </c>
       <c r="S22" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T22" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T22" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U22" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V22" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W22" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W22" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X22" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-22</v>
       </c>
-      <c r="X22" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y22" s="61" t="s">
-        <v>266</v>
+      <c r="Y22" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z22" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA22" s="30" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA22" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB22" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC22" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="56">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E23" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F23" s="62" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G23" s="63" t="s">
         <v>9</v>
@@ -4359,65 +4503,71 @@
         <v>Luminária</v>
       </c>
       <c r="O23" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Plafon</v>
       </c>
       <c r="P23" s="30" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q23" s="30" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="R23" s="30" t="s">
-        <v>9</v>
+        <v>171</v>
       </c>
       <c r="S23" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T23" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T23" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U23" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V23" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W23" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W23" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X23" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-23</v>
       </c>
-      <c r="X23" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y23" s="61" t="s">
-        <v>266</v>
+      <c r="Y23" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z23" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA23" s="30" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA23" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB23" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC23" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="56">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E24" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F24" s="62" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G24" s="63" t="s">
         <v>9</v>
@@ -4447,65 +4597,71 @@
         <v>Luminária</v>
       </c>
       <c r="O24" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Sensorizada</v>
       </c>
       <c r="P24" s="30" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q24" s="30" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="R24" s="30" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="S24" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T24" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T24" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U24" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V24" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W24" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W24" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X24" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-24</v>
       </c>
-      <c r="X24" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y24" s="61" t="s">
-        <v>266</v>
+      <c r="Y24" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z24" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA24" s="30" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA24" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB24" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC24" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="56">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E25" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F25" s="62" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G25" s="63" t="s">
         <v>9</v>
@@ -4535,65 +4691,71 @@
         <v>Luminária</v>
       </c>
       <c r="O25" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Spot</v>
       </c>
       <c r="P25" s="30" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Q25" s="30" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R25" s="30" t="s">
-        <v>9</v>
+        <v>173</v>
       </c>
       <c r="S25" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T25" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T25" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U25" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V25" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W25" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W25" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X25" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-25</v>
       </c>
-      <c r="X25" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y25" s="61" t="s">
-        <v>268</v>
+      <c r="Y25" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z25" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA25" s="30" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA25" s="61" t="s">
+        <v>266</v>
+      </c>
+      <c r="AB25" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC25" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="56">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E26" s="43" t="s">
         <v>45</v>
       </c>
       <c r="F26" s="62" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G26" s="63" t="s">
         <v>9</v>
@@ -4623,153 +4785,165 @@
         <v>Luminária</v>
       </c>
       <c r="O26" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Luz.Trilho</v>
       </c>
       <c r="P26" s="30" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Q26" s="30" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="R26" s="30" t="s">
-        <v>9</v>
+        <v>174</v>
       </c>
       <c r="S26" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T26" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T26" s="30" t="s">
-        <v>186</v>
-      </c>
       <c r="U26" s="30" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="V26" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W26" s="58" t="str">
+        <v>238</v>
+      </c>
+      <c r="W26" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X26" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-26</v>
       </c>
-      <c r="X26" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y26" s="61" t="s">
-        <v>266</v>
+      <c r="Y26" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z26" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA26" s="30" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA26" s="61" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB26" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC26" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="56">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E27" s="43" t="s">
+        <v>210</v>
+      </c>
+      <c r="F27" s="62" t="s">
+        <v>240</v>
+      </c>
+      <c r="G27" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L27" s="34" t="str">
+        <f t="shared" ref="L27" si="16">CONCATENATE("", C27)</f>
+        <v>LuminoTécnicos</v>
+      </c>
+      <c r="M27" s="34" t="str">
+        <f t="shared" ref="M27" si="17">CONCATENATE("", D27)</f>
+        <v>Elemento.Iluminação</v>
+      </c>
+      <c r="N27" s="34" t="str">
+        <f t="shared" ref="N27" si="18">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E27),"."," ")," De "," de "))</f>
+        <v>Acessórios de Iluminação</v>
+      </c>
+      <c r="O27" s="30" t="str">
+        <f t="shared" ref="O27" si="19">IF(ISNUMBER(FIND("Ifc",F27)),CONCATENATE("Classe IFC:   ",F27),CONCATENATE("",F27))</f>
+        <v>Acessório.Luz</v>
+      </c>
+      <c r="P27" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="E27" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="F27" s="62" t="s">
-        <v>242</v>
-      </c>
-      <c r="G27" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="I27" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="J27" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="K27" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="L27" s="34" t="str">
-        <f t="shared" ref="L27" si="17">CONCATENATE("", C27)</f>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M27" s="34" t="str">
-        <f t="shared" ref="M27" si="18">CONCATENATE("", D27)</f>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N27" s="34" t="str">
-        <f t="shared" ref="N27" si="19">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E27),"."," ")," De "," de "))</f>
-        <v>Acessórios de Iluminação</v>
-      </c>
-      <c r="O27" s="30" t="str">
-        <f t="shared" ref="O27" si="20">IF(ISNUMBER(FIND("Ifc",F27)),CONCATENATE("Classe IFC:   ",F27),CONCATENATE("",F27))</f>
-        <v>Acessório.Luz</v>
-      </c>
-      <c r="P27" s="30" t="s">
+      <c r="Q27" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="R27" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="S27" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T27" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="U27" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="V27" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="W27" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="Q27" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="R27" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S27" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="T27" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="U27" s="30" t="s">
-        <v>240</v>
-      </c>
-      <c r="V27" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W27" s="58" t="str">
+      <c r="X27" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-27</v>
       </c>
-      <c r="X27" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y27" s="61" t="s">
-        <v>234</v>
+      <c r="Y27" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z27" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA27" s="30" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AA27" s="61" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB27" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC27" s="30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="56">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F28" s="62" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G28" s="63" t="s">
         <v>9</v>
@@ -4799,65 +4973,71 @@
         <v>Analítico de Luz</v>
       </c>
       <c r="O28" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Ponto.Iluminado</v>
       </c>
       <c r="P28" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q28" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="Q28" s="30" t="s">
-        <v>193</v>
-      </c>
       <c r="R28" s="30" t="s">
-        <v>9</v>
+        <v>195</v>
       </c>
       <c r="S28" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T28" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T28" s="30" t="s">
-        <v>187</v>
-      </c>
       <c r="U28" s="30" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="V28" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W28" s="58" t="str">
+        <v>234</v>
+      </c>
+      <c r="W28" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X28" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-28</v>
       </c>
-      <c r="X28" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="Y28" s="30" t="s">
-        <v>9</v>
+        <v>275</v>
       </c>
       <c r="Z28" s="30" t="s">
-        <v>9</v>
+        <v>275</v>
       </c>
       <c r="AA28" s="30" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AB28" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC28" s="30" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="56">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F29" s="62" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G29" s="63" t="s">
         <v>9</v>
@@ -4887,65 +5067,71 @@
         <v>Analítico de Luz</v>
       </c>
       <c r="O29" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Linha.Iluminada</v>
       </c>
       <c r="P29" s="30" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="Q29" s="30" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="R29" s="30" t="s">
-        <v>9</v>
+        <v>196</v>
       </c>
       <c r="S29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T29" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T29" s="30" t="s">
-        <v>187</v>
-      </c>
       <c r="U29" s="30" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="V29" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W29" s="58" t="str">
+        <v>234</v>
+      </c>
+      <c r="W29" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X29" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-29</v>
       </c>
-      <c r="X29" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="Y29" s="30" t="s">
-        <v>9</v>
+        <v>275</v>
       </c>
       <c r="Z29" s="30" t="s">
-        <v>9</v>
+        <v>275</v>
       </c>
       <c r="AA29" s="30" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>275</v>
+      </c>
+      <c r="AB29" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC29" s="30" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="56">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E30" s="43" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F30" s="62" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G30" s="63" t="s">
         <v>9</v>
@@ -4975,49 +5161,55 @@
         <v>Analítico de Luz</v>
       </c>
       <c r="O30" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>Area.Iluminada</v>
       </c>
       <c r="P30" s="30" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="Q30" s="30" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="R30" s="30" t="s">
-        <v>9</v>
+        <v>197</v>
       </c>
       <c r="S30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T30" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="T30" s="30" t="s">
-        <v>187</v>
-      </c>
       <c r="U30" s="30" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="V30" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="W30" s="58" t="str">
+        <v>234</v>
+      </c>
+      <c r="W30" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X30" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Key-ILUM-30</v>
       </c>
-      <c r="X30" s="30" t="s">
-        <v>9</v>
-      </c>
       <c r="Y30" s="30" t="s">
-        <v>9</v>
+        <v>275</v>
       </c>
       <c r="Z30" s="30" t="s">
-        <v>9</v>
+        <v>275</v>
       </c>
       <c r="AA30" s="30" t="s">
-        <v>199</v>
+        <v>275</v>
+      </c>
+      <c r="AB30" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="AC30" s="30" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA924">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC924">
     <sortCondition ref="F2:F924"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5026,7 +5218,7 @@
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:O1 R1:X1 Z1:AA1 AA4:AA30">
+  <conditionalFormatting sqref="A1:O1 R1:Y1 R4:R30 AC1">
     <cfRule type="cellIs" dxfId="19" priority="49" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -5051,15 +5243,15 @@
     <cfRule type="duplicateValues" dxfId="12" priority="244"/>
     <cfRule type="duplicateValues" dxfId="11" priority="1457"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X4:X27">
+  <conditionalFormatting sqref="Y4:Y27">
     <cfRule type="containsText" dxfId="10" priority="43" operator="containsText" text="null">
-      <formula>NOT(ISERROR(SEARCH("null",X4)))</formula>
+      <formula>NOT(ISERROR(SEARCH("null",Y4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y25">
+  <conditionalFormatting sqref="AA25">
     <cfRule type="duplicateValues" dxfId="9" priority="40"/>
     <cfRule type="containsText" dxfId="8" priority="41" operator="containsText" text="null">
-      <formula>NOT(ISERROR(SEARCH("null",Y25)))</formula>
+      <formula>NOT(ISERROR(SEARCH("null",AA25)))</formula>
     </cfRule>
     <cfRule type="duplicateValues" dxfId="7" priority="42"/>
   </conditionalFormatting>
@@ -5382,10 +5574,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D2" s="51" t="s">
         <v>9</v>
@@ -5397,7 +5589,7 @@
         <v>79</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H2" s="50" t="s">
         <v>9</v>
@@ -5441,28 +5633,28 @@
         <v>3</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D3" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E3" s="55" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F3" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H3" s="50" t="s">
         <v>79</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J3" s="50" t="s">
         <v>9</v>
@@ -5477,16 +5669,16 @@
         <v>9</v>
       </c>
       <c r="N3" s="50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O3" s="25" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P3" s="50" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q3" s="25" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="R3" s="50" t="s">
         <v>9</v>
@@ -5500,28 +5692,28 @@
         <v>4</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D4" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E4" s="55" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H4" s="50" t="s">
         <v>79</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J4" s="50" t="s">
         <v>9</v>
@@ -5536,16 +5728,16 @@
         <v>9</v>
       </c>
       <c r="N4" s="50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O4" s="25" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P4" s="50" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="R4" s="50" t="s">
         <v>9</v>
@@ -5559,28 +5751,28 @@
         <v>5</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H5" s="50" t="s">
         <v>79</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J5" s="50" t="s">
         <v>9</v>
@@ -5595,16 +5787,16 @@
         <v>9</v>
       </c>
       <c r="N5" s="50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O5" s="25" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P5" s="50" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q5" s="25" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="R5" s="50" t="s">
         <v>9</v>
@@ -5618,28 +5810,28 @@
         <v>6</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H6" s="50" t="s">
         <v>79</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J6" s="50" t="s">
         <v>9</v>
@@ -5654,16 +5846,16 @@
         <v>9</v>
       </c>
       <c r="N6" s="50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O6" s="25" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P6" s="50" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q6" s="25" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="R6" s="50" t="s">
         <v>9</v>
@@ -5677,58 +5869,58 @@
         <v>7</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D7" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E7" s="55" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F7" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H7" s="50" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J7" s="50" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L7" s="50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N7" s="50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P7" s="50" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q7" s="25" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="R7" s="50" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S7" s="25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -5736,58 +5928,58 @@
         <v>8</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D8" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E8" s="55" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F8" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H8" s="50" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J8" s="50" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L8" s="50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N8" s="50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O8" s="25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P8" s="50" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q8" s="25" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="R8" s="50" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S8" s="25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -5795,58 +5987,58 @@
         <v>9</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D9" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F9" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H9" s="50" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J9" s="50" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K9" s="25" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L9" s="50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M9" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N9" s="50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O9" s="25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P9" s="50" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q9" s="25" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="R9" s="50" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S9" s="25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -5854,58 +6046,58 @@
         <v>10</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D10" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E10" s="55" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F10" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H10" s="50" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J10" s="50" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K10" s="25" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L10" s="50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M10" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N10" s="50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O10" s="25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P10" s="50" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q10" s="25" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="R10" s="50" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S10" s="25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -5913,58 +6105,58 @@
         <v>11</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C11" s="54" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D11" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E11" s="55" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F11" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J11" s="50" t="s">
+        <v>217</v>
+      </c>
+      <c r="K11" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="K11" s="25" t="s">
-        <v>221</v>
-      </c>
       <c r="L11" s="50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M11" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N11" s="50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O11" s="25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P11" s="50" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q11" s="25" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="R11" s="50" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S11" s="25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -5972,58 +6164,58 @@
         <v>12</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D12" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E12" s="55" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F12" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H12" s="50" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J12" s="50" t="s">
+        <v>217</v>
+      </c>
+      <c r="K12" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="K12" s="25" t="s">
-        <v>221</v>
-      </c>
       <c r="L12" s="50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M12" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N12" s="50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O12" s="25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P12" s="50" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q12" s="25" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="R12" s="50" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S12" s="25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6031,58 +6223,58 @@
         <v>13</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D13" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E13" s="55" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F13" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J13" s="50" t="s">
+        <v>217</v>
+      </c>
+      <c r="K13" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="K13" s="25" t="s">
-        <v>221</v>
-      </c>
       <c r="L13" s="50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M13" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N13" s="50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O13" s="25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P13" s="50" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q13" s="25" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="R13" s="50" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S13" s="25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6090,58 +6282,58 @@
         <v>14</v>
       </c>
       <c r="B14" s="48" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D14" s="51" t="s">
         <v>84</v>
       </c>
       <c r="E14" s="55" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F14" s="23" t="s">
         <v>79</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H14" s="50" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J14" s="50" t="s">
+        <v>217</v>
+      </c>
+      <c r="K14" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="K14" s="25" t="s">
-        <v>221</v>
-      </c>
       <c r="L14" s="50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M14" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N14" s="50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O14" s="25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P14" s="50" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q14" s="25" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="R14" s="50" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="S14" s="25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/Versão5/SIS/Ontologia_Luminotecnica.xlsx
+++ b/Versão5/SIS/Ontologia_Luminotecnica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718E354B-CF9E-48B6-9FFD-18E09C94FC8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F728C893-DDB7-4638-989A-1AF9815BE7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="283">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -899,13 +899,28 @@
     <t>Atributo IFC</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>Parâmetro Rvt</t>
   </si>
   <si>
     <t>Categoria Rvt</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
   </si>
 </sst>
 </file>
@@ -996,7 +1011,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1135,6 +1150,12 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1248,7 +1269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1441,11 +1462,129 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="31">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1625,14 +1764,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2075,14 +2206,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" customWidth="1"/>
-    <col min="2" max="2" width="33.69140625" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>46</v>
       </c>
@@ -2093,7 +2224,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>48</v>
       </c>
@@ -2104,7 +2235,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>50</v>
       </c>
@@ -2115,7 +2246,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
@@ -2126,7 +2257,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -2138,7 +2269,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -2150,7 +2281,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
@@ -2161,7 +2292,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="38" t="s">
         <v>56</v>
       </c>
@@ -2172,7 +2303,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
@@ -2183,7 +2314,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
@@ -2194,7 +2325,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
@@ -2205,7 +2336,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
@@ -2216,7 +2347,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
@@ -2227,7 +2358,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -2238,7 +2369,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
@@ -2249,7 +2380,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
@@ -2260,7 +2391,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
@@ -2271,19 +2402,19 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46253.808837384262</v>
+        <v>46260.36117916667</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>69</v>
       </c>
@@ -2294,7 +2425,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
@@ -2305,7 +2436,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>72</v>
       </c>
@@ -2316,7 +2447,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>73</v>
       </c>
@@ -2327,7 +2458,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>74</v>
       </c>
@@ -2338,7 +2469,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>88</v>
       </c>
@@ -2358,38 +2489,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC30"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC31"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.23046875" style="59" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.69140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.3828125" style="59" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.15234375" style="59" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.69140625" style="64" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.4609375" style="59" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.69140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.3828125" style="59" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.23046875" style="59" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.69140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="28.69140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.921875" style="59" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.921875" style="59" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6" style="59" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.3828125" style="59" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.921875" style="59" customWidth="1"/>
-    <col min="23" max="23" width="4.921875" style="59" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.69140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10" style="59" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.765625" style="59" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16.84375" style="65" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="64" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.5703125" style="59" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="38.5703125" style="59" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="39" style="59" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.85546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.85546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.85546875" style="65" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="59" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.07421875" style="59" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="59"/>
+    <col min="29" max="29" width="7.28515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
         <v>154</v>
       </c>
@@ -2463,10 +2594,10 @@
         <v>8</v>
       </c>
       <c r="Y1" s="36" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Z1" s="36" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AA1" s="36" t="s">
         <v>273</v>
@@ -2478,7 +2609,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="56">
         <v>2</v>
       </c>
@@ -2555,26 +2686,26 @@
         <v>237</v>
       </c>
       <c r="X2" s="58" t="str">
-        <f t="shared" ref="X2:X30" si="6">CONCATENATE("Key-ILUM-",A2)</f>
+        <f t="shared" ref="X2:X31" si="6">CONCATENATE("Key-ILUM-",A2)</f>
         <v>Key-ILUM-2</v>
       </c>
       <c r="Y2" s="61" t="s">
         <v>208</v>
       </c>
-      <c r="Z2" s="30" t="s">
-        <v>275</v>
+      <c r="Z2" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA2" s="61" t="s">
         <v>209</v>
       </c>
-      <c r="AB2" s="30" t="s">
-        <v>275</v>
+      <c r="AB2" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC2" s="30" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="56">
         <v>3</v>
       </c>
@@ -2657,20 +2788,20 @@
       <c r="Y3" s="61" t="s">
         <v>208</v>
       </c>
-      <c r="Z3" s="30" t="s">
-        <v>275</v>
+      <c r="Z3" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA3" s="61" t="s">
         <v>209</v>
       </c>
-      <c r="AB3" s="30" t="s">
-        <v>275</v>
+      <c r="AB3" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC3" s="30" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="56">
         <v>4</v>
       </c>
@@ -2751,20 +2882,20 @@
       <c r="Y4" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z4" s="30" t="s">
-        <v>275</v>
+      <c r="Z4" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA4" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB4" s="30" t="s">
-        <v>275</v>
+      <c r="AB4" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC4" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="56">
         <v>5</v>
       </c>
@@ -2845,20 +2976,20 @@
       <c r="Y5" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z5" s="30" t="s">
-        <v>275</v>
+      <c r="Z5" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA5" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB5" s="30" t="s">
-        <v>275</v>
+      <c r="AB5" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC5" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="56">
         <v>6</v>
       </c>
@@ -2939,20 +3070,20 @@
       <c r="Y6" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z6" s="30" t="s">
-        <v>275</v>
+      <c r="Z6" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA6" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB6" s="30" t="s">
-        <v>275</v>
+      <c r="AB6" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC6" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="56">
         <v>7</v>
       </c>
@@ -3033,20 +3164,20 @@
       <c r="Y7" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z7" s="30" t="s">
-        <v>275</v>
+      <c r="Z7" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA7" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB7" s="30" t="s">
-        <v>275</v>
+      <c r="AB7" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC7" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="56">
         <v>8</v>
       </c>
@@ -3127,20 +3258,20 @@
       <c r="Y8" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z8" s="30" t="s">
-        <v>275</v>
+      <c r="Z8" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA8" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB8" s="30" t="s">
-        <v>275</v>
+      <c r="AB8" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC8" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="56">
         <v>9</v>
       </c>
@@ -3221,20 +3352,20 @@
       <c r="Y9" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z9" s="30" t="s">
-        <v>275</v>
+      <c r="Z9" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA9" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB9" s="30" t="s">
-        <v>275</v>
+      <c r="AB9" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC9" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="56">
         <v>10</v>
       </c>
@@ -3315,20 +3446,20 @@
       <c r="Y10" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z10" s="30" t="s">
-        <v>275</v>
+      <c r="Z10" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA10" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB10" s="30" t="s">
-        <v>275</v>
+      <c r="AB10" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC10" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56">
         <v>11</v>
       </c>
@@ -3409,20 +3540,20 @@
       <c r="Y11" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z11" s="30" t="s">
-        <v>275</v>
+      <c r="Z11" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA11" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB11" s="30" t="s">
-        <v>275</v>
+      <c r="AB11" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC11" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56">
         <v>12</v>
       </c>
@@ -3503,20 +3634,20 @@
       <c r="Y12" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z12" s="30" t="s">
-        <v>275</v>
+      <c r="Z12" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA12" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB12" s="30" t="s">
-        <v>275</v>
+      <c r="AB12" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC12" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56">
         <v>13</v>
       </c>
@@ -3597,20 +3728,20 @@
       <c r="Y13" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z13" s="30" t="s">
-        <v>275</v>
+      <c r="Z13" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA13" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB13" s="30" t="s">
-        <v>275</v>
+      <c r="AB13" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC13" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="56">
         <v>14</v>
       </c>
@@ -3691,20 +3822,20 @@
       <c r="Y14" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z14" s="30" t="s">
-        <v>275</v>
+      <c r="Z14" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA14" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB14" s="30" t="s">
-        <v>275</v>
+      <c r="AB14" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC14" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="56">
         <v>15</v>
       </c>
@@ -3785,20 +3916,20 @@
       <c r="Y15" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z15" s="30" t="s">
-        <v>275</v>
+      <c r="Z15" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA15" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB15" s="30" t="s">
-        <v>275</v>
+      <c r="AB15" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC15" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="56">
         <v>16</v>
       </c>
@@ -3879,20 +4010,20 @@
       <c r="Y16" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z16" s="30" t="s">
-        <v>275</v>
+      <c r="Z16" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA16" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB16" s="30" t="s">
-        <v>275</v>
+      <c r="AB16" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC16" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="56">
         <v>17</v>
       </c>
@@ -3973,20 +4104,20 @@
       <c r="Y17" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z17" s="30" t="s">
-        <v>275</v>
+      <c r="Z17" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA17" s="61" t="s">
         <v>265</v>
       </c>
-      <c r="AB17" s="30" t="s">
-        <v>275</v>
+      <c r="AB17" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC17" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="56">
         <v>18</v>
       </c>
@@ -4067,20 +4198,20 @@
       <c r="Y18" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z18" s="30" t="s">
-        <v>275</v>
+      <c r="Z18" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA18" s="61" t="s">
         <v>265</v>
       </c>
-      <c r="AB18" s="30" t="s">
-        <v>275</v>
+      <c r="AB18" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC18" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="56">
         <v>19</v>
       </c>
@@ -4161,20 +4292,20 @@
       <c r="Y19" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z19" s="30" t="s">
-        <v>275</v>
+      <c r="Z19" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA19" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB19" s="30" t="s">
-        <v>275</v>
+      <c r="AB19" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC19" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="56">
         <v>20</v>
       </c>
@@ -4255,20 +4386,20 @@
       <c r="Y20" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z20" s="30" t="s">
-        <v>275</v>
+      <c r="Z20" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA20" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB20" s="30" t="s">
-        <v>275</v>
+      <c r="AB20" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC20" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="56">
         <v>21</v>
       </c>
@@ -4349,20 +4480,20 @@
       <c r="Y21" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z21" s="30" t="s">
-        <v>275</v>
+      <c r="Z21" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA21" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB21" s="30" t="s">
-        <v>275</v>
+      <c r="AB21" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC21" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="56">
         <v>22</v>
       </c>
@@ -4443,20 +4574,20 @@
       <c r="Y22" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z22" s="30" t="s">
-        <v>275</v>
+      <c r="Z22" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA22" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB22" s="30" t="s">
-        <v>275</v>
+      <c r="AB22" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC22" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="56">
         <v>23</v>
       </c>
@@ -4537,20 +4668,20 @@
       <c r="Y23" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z23" s="30" t="s">
-        <v>275</v>
+      <c r="Z23" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA23" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB23" s="30" t="s">
-        <v>275</v>
+      <c r="AB23" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC23" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="56">
         <v>24</v>
       </c>
@@ -4631,20 +4762,20 @@
       <c r="Y24" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z24" s="30" t="s">
-        <v>275</v>
+      <c r="Z24" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA24" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB24" s="30" t="s">
-        <v>275</v>
+      <c r="AB24" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC24" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="56">
         <v>25</v>
       </c>
@@ -4725,20 +4856,20 @@
       <c r="Y25" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z25" s="30" t="s">
-        <v>275</v>
+      <c r="Z25" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA25" s="61" t="s">
         <v>266</v>
       </c>
-      <c r="AB25" s="30" t="s">
-        <v>275</v>
+      <c r="AB25" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC25" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="56">
         <v>26</v>
       </c>
@@ -4819,20 +4950,20 @@
       <c r="Y26" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z26" s="30" t="s">
-        <v>275</v>
+      <c r="Z26" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA26" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB26" s="30" t="s">
-        <v>275</v>
+      <c r="AB26" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC26" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="56">
         <v>27</v>
       </c>
@@ -4913,20 +5044,20 @@
       <c r="Y27" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z27" s="30" t="s">
-        <v>275</v>
+      <c r="Z27" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA27" s="61" t="s">
         <v>232</v>
       </c>
-      <c r="AB27" s="30" t="s">
-        <v>275</v>
+      <c r="AB27" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC27" s="30" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="56">
         <v>28</v>
       </c>
@@ -5004,23 +5135,23 @@
         <f t="shared" si="6"/>
         <v>Key-ILUM-28</v>
       </c>
-      <c r="Y28" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="Z28" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="AA28" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="AB28" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="AC28" s="30" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y28" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z28" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA28" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB28" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC28" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="56">
         <v>29</v>
       </c>
@@ -5098,23 +5229,23 @@
         <f t="shared" si="6"/>
         <v>Key-ILUM-29</v>
       </c>
-      <c r="Y29" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="Z29" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="AA29" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="AB29" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="AC29" s="30" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y29" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z29" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA29" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB29" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC29" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="56">
         <v>30</v>
       </c>
@@ -5192,20 +5323,119 @@
         <f t="shared" si="6"/>
         <v>Key-ILUM-30</v>
       </c>
-      <c r="Y30" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="Z30" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="AA30" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="AB30" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="AC30" s="30" t="s">
-        <v>275</v>
+      <c r="Y30" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z30" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA30" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB30" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC30" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="56">
+        <v>31</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C31" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="D31" s="62" t="s">
+        <v>279</v>
+      </c>
+      <c r="E31" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="F31" s="62" t="s">
+        <v>281</v>
+      </c>
+      <c r="G31" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I31" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K31" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L31" s="34" t="str">
+        <f t="shared" ref="L31:O31" si="20">SUBSTITUTE(CONCATENATE("", C31), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M31" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N31" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>Macros</v>
+      </c>
+      <c r="O31" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P31" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q31" s="66" t="str">
+        <f t="shared" ref="Q31" si="21">_xlfn.TRANSLATE(P31,"pt","es")</f>
+        <v>Aplicación Revit</v>
+      </c>
+      <c r="R31" s="66" t="str">
+        <f t="shared" ref="R31" si="22">_xlfn.TRANSLATE(P31,"pt","en")</f>
+        <v>Revit App</v>
+      </c>
+      <c r="S31" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T31" s="30" t="str">
+        <f t="shared" ref="T31:V31" si="23">SUBSTITUTE(C31, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U31" s="30" t="str">
+        <f t="shared" si="23"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V31" s="67" t="str">
+        <f t="shared" si="23"/>
+        <v>Macros</v>
+      </c>
+      <c r="W31" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X31" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-ILUM-31</v>
+      </c>
+      <c r="Y31" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z31" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA31" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB31" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC31" s="68" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -5213,47 +5443,67 @@
     <sortCondition ref="F2:F924"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B30">
-    <cfRule type="cellIs" dxfId="20" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B30 A31">
+    <cfRule type="cellIs" dxfId="0" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:O1 R1:Y1 R4:R30 AC1">
-    <cfRule type="cellIs" dxfId="19" priority="49" operator="equal">
+  <conditionalFormatting sqref="A1:O1 R1:Y1 AC1 R4:R30">
+    <cfRule type="cellIs" dxfId="30" priority="59" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="18" priority="1485"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="1495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="duplicateValues" dxfId="17" priority="1507"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1517"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="1478"/>
+  <conditionalFormatting sqref="F4:F30 F32:F1048576">
+    <cfRule type="duplicateValues" dxfId="27" priority="1488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26 F28:F30">
-    <cfRule type="duplicateValues" dxfId="15" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27">
-    <cfRule type="duplicateValues" dxfId="14" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31:F1048576 F4:F25">
-    <cfRule type="duplicateValues" dxfId="13" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="244"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="1457"/>
+  <conditionalFormatting sqref="F32:F1048576 F4:F25">
+    <cfRule type="duplicateValues" dxfId="24" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1467"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y4:Y27">
-    <cfRule type="containsText" dxfId="10" priority="43" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="21" priority="53" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA25">
-    <cfRule type="duplicateValues" dxfId="9" priority="40"/>
-    <cfRule type="containsText" dxfId="8" priority="41" operator="containsText" text="null">
+    <cfRule type="duplicateValues" dxfId="20" priority="50"/>
+    <cfRule type="containsText" dxfId="19" priority="51" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",AA25)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="7" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31">
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q31">
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R31">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -5266,15 +5516,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -5339,7 +5589,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5404,7 +5654,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -5471,7 +5721,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5487,30 +5737,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="64.84375" customWidth="1"/>
-    <col min="8" max="8" width="8.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.53515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.3828125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.3046875" customWidth="1"/>
-    <col min="14" max="14" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.3046875" customWidth="1"/>
-    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.69140625" customWidth="1"/>
-    <col min="18" max="18" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64.85546875" customWidth="1"/>
+    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" customWidth="1"/>
+    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.7109375" customWidth="1"/>
+    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -5569,7 +5819,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -5628,7 +5878,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21">
         <v>3</v>
       </c>
@@ -5687,7 +5937,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21">
         <v>4</v>
       </c>
@@ -5746,7 +5996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21">
         <v>5</v>
       </c>
@@ -5805,7 +6055,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21">
         <v>6</v>
       </c>
@@ -5864,7 +6114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21">
         <v>7</v>
       </c>
@@ -5923,7 +6173,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21">
         <v>8</v>
       </c>
@@ -5982,7 +6232,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21">
         <v>9</v>
       </c>
@@ -6041,7 +6291,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21">
         <v>10</v>
       </c>
@@ -6100,7 +6350,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21">
         <v>11</v>
       </c>
@@ -6159,7 +6409,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="21">
         <v>12</v>
       </c>
@@ -6218,7 +6468,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21">
         <v>13</v>
       </c>
@@ -6277,7 +6527,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21">
         <v>14</v>
       </c>
@@ -6346,15 +6596,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="27" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -6377,7 +6627,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -6406,22 +6656,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SIS/Ontologia_Luminotecnica.xlsx
+++ b/Versão5/SIS/Ontologia_Luminotecnica.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F728C893-DDB7-4638-989A-1AF9815BE7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C5D343-EDEE-46BB-82E7-B1FF36A3A2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -1478,113 +1478,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="30">
     <dxf>
       <font>
         <b val="0"/>
@@ -1764,6 +1658,104 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2206,14 +2198,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="33.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.69140625" customWidth="1"/>
+    <col min="2" max="2" width="33.69140625" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>46</v>
       </c>
@@ -2224,7 +2216,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>48</v>
       </c>
@@ -2235,7 +2227,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>50</v>
       </c>
@@ -2246,7 +2238,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
@@ -2257,7 +2249,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -2269,7 +2261,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -2281,7 +2273,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
@@ -2292,7 +2284,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="38" t="s">
         <v>56</v>
       </c>
@@ -2303,7 +2295,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
@@ -2314,7 +2306,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
@@ -2325,7 +2317,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
@@ -2336,7 +2328,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
@@ -2347,7 +2339,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
@@ -2358,7 +2350,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -2369,7 +2361,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
@@ -2380,7 +2372,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
@@ -2391,7 +2383,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
@@ -2402,19 +2394,19 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46260.36117916667</v>
+        <v>46264.570535416664</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>69</v>
       </c>
@@ -2425,7 +2417,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
@@ -2436,7 +2428,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>72</v>
       </c>
@@ -2447,7 +2439,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>73</v>
       </c>
@@ -2458,7 +2450,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>74</v>
       </c>
@@ -2469,7 +2461,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>88</v>
       </c>
@@ -2490,37 +2482,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC31"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="64" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.5703125" style="59" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="59" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="38.5703125" style="59" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="59" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.15234375" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.3046875" style="59" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.15234375" style="59" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3828125" style="64" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.53515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.15234375" style="59" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.3046875" style="59" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.15234375" style="59" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="38.53515625" style="59" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="39" style="59" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.42578125" style="59" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.42578125" style="59" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16.85546875" style="65" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.84375" style="59" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.15234375" style="59" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.84375" style="59" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.84375" style="59" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.84375" style="65" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="59" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="59"/>
+    <col min="29" max="29" width="7.3046875" style="59" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="44" t="s">
         <v>154</v>
       </c>
@@ -2609,7 +2601,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="56">
         <v>2</v>
       </c>
@@ -2705,7 +2697,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="56">
         <v>3</v>
       </c>
@@ -2801,7 +2793,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="56">
         <v>4</v>
       </c>
@@ -2895,7 +2887,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="56">
         <v>5</v>
       </c>
@@ -2989,7 +2981,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="56">
         <v>6</v>
       </c>
@@ -3083,7 +3075,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="56">
         <v>7</v>
       </c>
@@ -3177,7 +3169,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="56">
         <v>8</v>
       </c>
@@ -3271,7 +3263,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="56">
         <v>9</v>
       </c>
@@ -3365,7 +3357,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="56">
         <v>10</v>
       </c>
@@ -3459,7 +3451,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="56">
         <v>11</v>
       </c>
@@ -3553,7 +3545,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="56">
         <v>12</v>
       </c>
@@ -3647,7 +3639,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="56">
         <v>13</v>
       </c>
@@ -3741,7 +3733,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="56">
         <v>14</v>
       </c>
@@ -3835,7 +3827,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="56">
         <v>15</v>
       </c>
@@ -3929,7 +3921,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="56">
         <v>16</v>
       </c>
@@ -4023,7 +4015,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="56">
         <v>17</v>
       </c>
@@ -4117,7 +4109,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="56">
         <v>18</v>
       </c>
@@ -4211,7 +4203,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="56">
         <v>19</v>
       </c>
@@ -4305,7 +4297,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="56">
         <v>20</v>
       </c>
@@ -4399,7 +4391,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="56">
         <v>21</v>
       </c>
@@ -4493,7 +4485,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="56">
         <v>22</v>
       </c>
@@ -4587,7 +4579,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="56">
         <v>23</v>
       </c>
@@ -4681,7 +4673,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="56">
         <v>24</v>
       </c>
@@ -4775,7 +4767,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="56">
         <v>25</v>
       </c>
@@ -4869,7 +4861,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="56">
         <v>26</v>
       </c>
@@ -4963,7 +4955,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="56">
         <v>27</v>
       </c>
@@ -5057,7 +5049,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="56">
         <v>28</v>
       </c>
@@ -5151,7 +5143,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="56">
         <v>29</v>
       </c>
@@ -5245,7 +5237,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="56">
         <v>30</v>
       </c>
@@ -5339,7 +5331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="56">
         <v>31</v>
       </c>
@@ -5350,10 +5342,10 @@
         <v>278</v>
       </c>
       <c r="D31" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="E31" s="62" t="s">
         <v>279</v>
-      </c>
-      <c r="E31" s="62" t="s">
-        <v>280</v>
       </c>
       <c r="F31" s="62" t="s">
         <v>281</v>
@@ -5379,11 +5371,11 @@
       </c>
       <c r="M31" s="34" t="str">
         <f t="shared" si="20"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N31" s="34" t="str">
         <f t="shared" si="20"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O31" s="34" t="str">
         <f t="shared" si="20"/>
@@ -5409,11 +5401,11 @@
       </c>
       <c r="U31" s="30" t="str">
         <f t="shared" si="23"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V31" s="67" t="str">
         <f t="shared" si="23"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W31" s="30" t="s">
         <v>237</v>
@@ -5443,67 +5435,62 @@
     <sortCondition ref="F2:F924"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B30 A31">
-    <cfRule type="cellIs" dxfId="0" priority="16" operator="equal">
+  <conditionalFormatting sqref="A2:B31">
+    <cfRule type="cellIs" dxfId="29" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:O1 R1:Y1 AC1 R4:R30">
-    <cfRule type="cellIs" dxfId="30" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="59" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="29" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="duplicateValues" dxfId="28" priority="1517"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1517"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F30 F32:F1048576">
-    <cfRule type="duplicateValues" dxfId="27" priority="1488"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26 F28:F30">
-    <cfRule type="duplicateValues" dxfId="26" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27">
-    <cfRule type="duplicateValues" dxfId="25" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31">
+    <cfRule type="duplicateValues" dxfId="22" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F1048576 F4:F25">
-    <cfRule type="duplicateValues" dxfId="24" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="1467"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1467"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q31">
+    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R31">
+    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y4:Y27">
-    <cfRule type="containsText" dxfId="21" priority="53" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="10" priority="53" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA25">
-    <cfRule type="duplicateValues" dxfId="20" priority="50"/>
-    <cfRule type="containsText" dxfId="19" priority="51" operator="containsText" text="null">
+    <cfRule type="duplicateValues" dxfId="9" priority="50"/>
+    <cfRule type="containsText" dxfId="8" priority="51" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",AA25)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="18" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F31">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q31">
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R31">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="52"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -5516,15 +5503,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -5589,7 +5576,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5654,7 +5641,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -5721,7 +5708,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5737,30 +5724,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="64.85546875" customWidth="1"/>
-    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" customWidth="1"/>
-    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.28515625" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.7109375" customWidth="1"/>
-    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64.84375" customWidth="1"/>
+    <col min="8" max="8" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.53515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.3828125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.3046875" customWidth="1"/>
+    <col min="14" max="14" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.3046875" customWidth="1"/>
+    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.69140625" customWidth="1"/>
+    <col min="18" max="18" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -5819,7 +5806,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -5878,7 +5865,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="21">
         <v>3</v>
       </c>
@@ -5937,7 +5924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21">
         <v>4</v>
       </c>
@@ -5996,7 +5983,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="21">
         <v>5</v>
       </c>
@@ -6055,7 +6042,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="21">
         <v>6</v>
       </c>
@@ -6114,7 +6101,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="21">
         <v>7</v>
       </c>
@@ -6173,7 +6160,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="21">
         <v>8</v>
       </c>
@@ -6232,7 +6219,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="21">
         <v>9</v>
       </c>
@@ -6291,7 +6278,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="21">
         <v>10</v>
       </c>
@@ -6350,7 +6337,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="21">
         <v>11</v>
       </c>
@@ -6409,7 +6396,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="21">
         <v>12</v>
       </c>
@@ -6468,7 +6455,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="21">
         <v>13</v>
       </c>
@@ -6527,7 +6514,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="21">
         <v>14</v>
       </c>
@@ -6596,15 +6583,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="27" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="27" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -6627,7 +6614,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -6656,22 +6643,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="15" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SIS/Ontologia_Luminotecnica.xlsx
+++ b/Versão5/SIS/Ontologia_Luminotecnica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C5D343-EDEE-46BB-82E7-B1FF36A3A2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F166689-03B6-426C-9124-DAE9B33F947A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="303">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -917,10 +917,70 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1463,9 +1523,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1478,7 +1535,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="23">
     <dxf>
       <font>
         <b val="0"/>
@@ -1578,76 +1635,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2198,14 +2185,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" customWidth="1"/>
-    <col min="2" max="2" width="33.69140625" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>46</v>
       </c>
@@ -2216,7 +2203,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>48</v>
       </c>
@@ -2227,7 +2214,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>50</v>
       </c>
@@ -2238,7 +2225,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
@@ -2249,7 +2236,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -2261,7 +2248,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -2273,7 +2260,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
@@ -2284,7 +2271,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="38" t="s">
         <v>56</v>
       </c>
@@ -2295,7 +2282,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
@@ -2306,7 +2293,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
@@ -2317,7 +2304,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
@@ -2328,7 +2315,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
@@ -2339,7 +2326,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
@@ -2350,7 +2337,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -2361,7 +2348,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
@@ -2372,7 +2359,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
@@ -2383,7 +2370,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
@@ -2394,19 +2381,19 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46264.570535416664</v>
+        <v>46268.700817824072</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>69</v>
       </c>
@@ -2417,7 +2404,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
@@ -2428,7 +2415,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>72</v>
       </c>
@@ -2439,7 +2426,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>73</v>
       </c>
@@ -2450,7 +2437,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>74</v>
       </c>
@@ -2461,7 +2448,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>88</v>
       </c>
@@ -2481,38 +2468,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC31"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="59" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.15234375" style="59" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.3046875" style="59" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.15234375" style="59" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.3828125" style="64" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.53515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.15234375" style="59" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.3046875" style="59" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.15234375" style="59" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.3828125" style="59" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="38.53515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="64" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.5703125" style="59" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="38.5703125" style="59" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="39" style="59" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.84375" style="59" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.15234375" style="59" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.3828125" style="59" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.69140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.69140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.3828125" style="59" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.84375" style="59" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.84375" style="59" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16.84375" style="65" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8" style="59" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.85546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.85546875" style="65" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="59" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.3046875" style="59" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="59"/>
+    <col min="29" max="29" width="7.28515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="2.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
         <v>154</v>
       </c>
@@ -2600,8 +2588,11 @@
       <c r="AC1" s="36" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD1" s="36" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="56">
         <v>2</v>
       </c>
@@ -2678,26 +2669,29 @@
         <v>237</v>
       </c>
       <c r="X2" s="58" t="str">
-        <f t="shared" ref="X2:X31" si="6">CONCATENATE("Key-ILUM-",A2)</f>
+        <f t="shared" ref="X2:X35" si="6">CONCATENATE("Key-ILUM-",A2)</f>
         <v>Key-ILUM-2</v>
       </c>
       <c r="Y2" s="61" t="s">
         <v>208</v>
       </c>
-      <c r="Z2" s="68" t="s">
+      <c r="Z2" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA2" s="61" t="s">
         <v>209</v>
       </c>
-      <c r="AB2" s="68" t="s">
+      <c r="AB2" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC2" s="30" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD2" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="56">
         <v>3</v>
       </c>
@@ -2780,20 +2774,23 @@
       <c r="Y3" s="61" t="s">
         <v>208</v>
       </c>
-      <c r="Z3" s="68" t="s">
+      <c r="Z3" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA3" s="61" t="s">
         <v>209</v>
       </c>
-      <c r="AB3" s="68" t="s">
+      <c r="AB3" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC3" s="30" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD3" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="56">
         <v>4</v>
       </c>
@@ -2874,20 +2871,23 @@
       <c r="Y4" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z4" s="68" t="s">
+      <c r="Z4" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA4" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB4" s="68" t="s">
+      <c r="AB4" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC4" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD4" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="56">
         <v>5</v>
       </c>
@@ -2968,20 +2968,23 @@
       <c r="Y5" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z5" s="68" t="s">
+      <c r="Z5" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA5" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB5" s="68" t="s">
+      <c r="AB5" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC5" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD5" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="56">
         <v>6</v>
       </c>
@@ -3062,20 +3065,23 @@
       <c r="Y6" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z6" s="68" t="s">
+      <c r="Z6" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA6" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB6" s="68" t="s">
+      <c r="AB6" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC6" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD6" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="56">
         <v>7</v>
       </c>
@@ -3156,20 +3162,23 @@
       <c r="Y7" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z7" s="68" t="s">
+      <c r="Z7" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA7" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB7" s="68" t="s">
+      <c r="AB7" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC7" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD7" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="56">
         <v>8</v>
       </c>
@@ -3250,20 +3259,23 @@
       <c r="Y8" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z8" s="68" t="s">
+      <c r="Z8" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA8" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB8" s="68" t="s">
+      <c r="AB8" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC8" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD8" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="56">
         <v>9</v>
       </c>
@@ -3344,20 +3356,23 @@
       <c r="Y9" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z9" s="68" t="s">
+      <c r="Z9" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA9" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB9" s="68" t="s">
+      <c r="AB9" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC9" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD9" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="56">
         <v>10</v>
       </c>
@@ -3438,20 +3453,23 @@
       <c r="Y10" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z10" s="68" t="s">
+      <c r="Z10" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA10" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB10" s="68" t="s">
+      <c r="AB10" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC10" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD10" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56">
         <v>11</v>
       </c>
@@ -3532,20 +3550,23 @@
       <c r="Y11" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z11" s="68" t="s">
+      <c r="Z11" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA11" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB11" s="68" t="s">
+      <c r="AB11" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC11" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD11" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56">
         <v>12</v>
       </c>
@@ -3626,20 +3647,23 @@
       <c r="Y12" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z12" s="68" t="s">
+      <c r="Z12" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA12" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB12" s="68" t="s">
+      <c r="AB12" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC12" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD12" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56">
         <v>13</v>
       </c>
@@ -3720,20 +3744,23 @@
       <c r="Y13" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z13" s="68" t="s">
+      <c r="Z13" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA13" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB13" s="68" t="s">
+      <c r="AB13" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC13" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD13" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="56">
         <v>14</v>
       </c>
@@ -3814,20 +3841,23 @@
       <c r="Y14" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z14" s="68" t="s">
+      <c r="Z14" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA14" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB14" s="68" t="s">
+      <c r="AB14" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC14" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD14" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="56">
         <v>15</v>
       </c>
@@ -3908,20 +3938,23 @@
       <c r="Y15" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z15" s="68" t="s">
+      <c r="Z15" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA15" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB15" s="68" t="s">
+      <c r="AB15" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC15" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD15" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="56">
         <v>16</v>
       </c>
@@ -4002,20 +4035,23 @@
       <c r="Y16" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z16" s="68" t="s">
+      <c r="Z16" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA16" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB16" s="68" t="s">
+      <c r="AB16" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC16" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD16" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="56">
         <v>17</v>
       </c>
@@ -4096,20 +4132,23 @@
       <c r="Y17" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z17" s="68" t="s">
+      <c r="Z17" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA17" s="61" t="s">
         <v>265</v>
       </c>
-      <c r="AB17" s="68" t="s">
+      <c r="AB17" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC17" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD17" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="56">
         <v>18</v>
       </c>
@@ -4190,20 +4229,23 @@
       <c r="Y18" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z18" s="68" t="s">
+      <c r="Z18" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA18" s="61" t="s">
         <v>265</v>
       </c>
-      <c r="AB18" s="68" t="s">
+      <c r="AB18" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC18" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD18" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="56">
         <v>19</v>
       </c>
@@ -4284,20 +4326,23 @@
       <c r="Y19" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z19" s="68" t="s">
+      <c r="Z19" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA19" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB19" s="68" t="s">
+      <c r="AB19" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC19" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD19" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="56">
         <v>20</v>
       </c>
@@ -4378,20 +4423,23 @@
       <c r="Y20" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z20" s="68" t="s">
+      <c r="Z20" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA20" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB20" s="68" t="s">
+      <c r="AB20" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC20" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD20" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="56">
         <v>21</v>
       </c>
@@ -4472,20 +4520,23 @@
       <c r="Y21" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z21" s="68" t="s">
+      <c r="Z21" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA21" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB21" s="68" t="s">
+      <c r="AB21" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC21" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD21" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="56">
         <v>22</v>
       </c>
@@ -4566,20 +4617,23 @@
       <c r="Y22" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z22" s="68" t="s">
+      <c r="Z22" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA22" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB22" s="68" t="s">
+      <c r="AB22" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC22" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD22" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="56">
         <v>23</v>
       </c>
@@ -4660,20 +4714,23 @@
       <c r="Y23" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z23" s="68" t="s">
+      <c r="Z23" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA23" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB23" s="68" t="s">
+      <c r="AB23" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC23" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD23" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="56">
         <v>24</v>
       </c>
@@ -4754,20 +4811,23 @@
       <c r="Y24" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z24" s="68" t="s">
+      <c r="Z24" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA24" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB24" s="68" t="s">
+      <c r="AB24" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC24" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD24" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="56">
         <v>25</v>
       </c>
@@ -4848,20 +4908,23 @@
       <c r="Y25" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z25" s="68" t="s">
+      <c r="Z25" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA25" s="61" t="s">
         <v>266</v>
       </c>
-      <c r="AB25" s="68" t="s">
+      <c r="AB25" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC25" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD25" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="56">
         <v>26</v>
       </c>
@@ -4942,20 +5005,23 @@
       <c r="Y26" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z26" s="68" t="s">
+      <c r="Z26" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA26" s="61" t="s">
         <v>264</v>
       </c>
-      <c r="AB26" s="68" t="s">
+      <c r="AB26" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC26" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD26" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="56">
         <v>27</v>
       </c>
@@ -5036,20 +5102,23 @@
       <c r="Y27" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="Z27" s="68" t="s">
+      <c r="Z27" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA27" s="61" t="s">
         <v>232</v>
       </c>
-      <c r="AB27" s="68" t="s">
+      <c r="AB27" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC27" s="30" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD27" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="56">
         <v>28</v>
       </c>
@@ -5127,23 +5196,26 @@
         <f t="shared" si="6"/>
         <v>Key-ILUM-28</v>
       </c>
-      <c r="Y28" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z28" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA28" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB28" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC28" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD28" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="56">
         <v>29</v>
       </c>
@@ -5221,23 +5293,26 @@
         <f t="shared" si="6"/>
         <v>Key-ILUM-29</v>
       </c>
-      <c r="Y29" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z29" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA29" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB29" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC29" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD29" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="56">
         <v>30</v>
       </c>
@@ -5315,23 +5390,26 @@
         <f t="shared" si="6"/>
         <v>Key-ILUM-30</v>
       </c>
-      <c r="Y30" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z30" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA30" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB30" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC30" s="68" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Y30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD30" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="56">
         <v>31</v>
       </c>
@@ -5366,7 +5444,7 @@
         <v>9</v>
       </c>
       <c r="L31" s="34" t="str">
-        <f t="shared" ref="L31:O31" si="20">SUBSTITUTE(CONCATENATE("", C31), ".", " ")</f>
+        <f t="shared" ref="L31:O35" si="20">SUBSTITUTE(CONCATENATE("", C31), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M31" s="34" t="str">
@@ -5379,32 +5457,30 @@
       </c>
       <c r="O31" s="34" t="str">
         <f t="shared" si="20"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P31" s="30" t="s">
         <v>282</v>
       </c>
-      <c r="Q31" s="66" t="str">
-        <f t="shared" ref="Q31" si="21">_xlfn.TRANSLATE(P31,"pt","es")</f>
-        <v>Aplicación Revit</v>
-      </c>
-      <c r="R31" s="66" t="str">
-        <f t="shared" ref="R31" si="22">_xlfn.TRANSLATE(P31,"pt","en")</f>
-        <v>Revit App</v>
+      <c r="Q31" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="R31" s="30" t="s">
+        <v>284</v>
       </c>
       <c r="S31" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T31" s="30" t="str">
-        <f t="shared" ref="T31:V31" si="23">SUBSTITUTE(C31, ".", " ")</f>
+        <f t="shared" ref="T31:V35" si="21">SUBSTITUTE(C31, ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="U31" s="30" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>Macros</v>
       </c>
-      <c r="V31" s="67" t="str">
-        <f t="shared" si="23"/>
+      <c r="V31" s="66" t="str">
+        <f t="shared" si="21"/>
         <v>Métodos</v>
       </c>
       <c r="W31" s="30" t="s">
@@ -5414,19 +5490,422 @@
         <f t="shared" si="6"/>
         <v>Key-ILUM-31</v>
       </c>
-      <c r="Y31" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z31" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA31" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB31" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC31" s="68" t="s">
+      <c r="Y31" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z31" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA31" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB31" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC31" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD31" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="56">
+        <v>32</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C32" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="D32" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="E32" s="62" t="s">
+        <v>279</v>
+      </c>
+      <c r="F32" s="62" t="s">
+        <v>285</v>
+      </c>
+      <c r="G32" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I32" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J32" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K32" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L32" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>De API</v>
+      </c>
+      <c r="M32" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>Macros</v>
+      </c>
+      <c r="N32" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O32" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P32" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q32" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="R32" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="S32" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T32" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De API</v>
+      </c>
+      <c r="U32" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Macros</v>
+      </c>
+      <c r="V32" s="66" t="str">
+        <f t="shared" si="21"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W32" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X32" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-ILUM-32</v>
+      </c>
+      <c r="Y32" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z32" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA32" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB32" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC32" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD32" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="56">
+        <v>33</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C33" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="D33" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="E33" s="62" t="s">
+        <v>279</v>
+      </c>
+      <c r="F33" s="62" t="s">
+        <v>289</v>
+      </c>
+      <c r="G33" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I33" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J33" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L33" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>De API</v>
+      </c>
+      <c r="M33" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>Macros</v>
+      </c>
+      <c r="N33" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O33" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P33" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q33" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="R33" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="S33" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T33" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De API</v>
+      </c>
+      <c r="U33" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Macros</v>
+      </c>
+      <c r="V33" s="66" t="str">
+        <f t="shared" si="21"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W33" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X33" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-ILUM-33</v>
+      </c>
+      <c r="Y33" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z33" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA33" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB33" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC33" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD33" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="56">
+        <v>34</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C34" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="D34" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="E34" s="62" t="s">
+        <v>279</v>
+      </c>
+      <c r="F34" s="62" t="s">
+        <v>293</v>
+      </c>
+      <c r="G34" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I34" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J34" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K34" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L34" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>De API</v>
+      </c>
+      <c r="M34" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>Macros</v>
+      </c>
+      <c r="N34" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O34" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P34" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q34" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="R34" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="S34" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T34" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De API</v>
+      </c>
+      <c r="U34" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Macros</v>
+      </c>
+      <c r="V34" s="66" t="str">
+        <f t="shared" si="21"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W34" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X34" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-ILUM-34</v>
+      </c>
+      <c r="Y34" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z34" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA34" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB34" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC34" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD34" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="56">
+        <v>35</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C35" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="D35" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="E35" s="62" t="s">
+        <v>297</v>
+      </c>
+      <c r="F35" s="62" t="s">
+        <v>298</v>
+      </c>
+      <c r="G35" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I35" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J35" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K35" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L35" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>De API</v>
+      </c>
+      <c r="M35" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>Macros</v>
+      </c>
+      <c r="N35" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O35" s="34" t="str">
+        <f t="shared" si="20"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P35" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q35" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="R35" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="S35" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T35" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>De API</v>
+      </c>
+      <c r="U35" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Macros</v>
+      </c>
+      <c r="V35" s="66" t="str">
+        <f t="shared" si="21"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W35" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X35" s="58" t="str">
+        <f t="shared" si="6"/>
+        <v>Key-ILUM-35</v>
+      </c>
+      <c r="Y35" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z35" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA35" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB35" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC35" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD35" s="67" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5435,62 +5914,53 @@
     <sortCondition ref="F2:F924"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B31">
-    <cfRule type="cellIs" dxfId="29" priority="5" operator="equal">
+  <conditionalFormatting sqref="A2:B35">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:O1 R1:Y1 AC1 R4:R30">
-    <cfRule type="cellIs" dxfId="28" priority="59" operator="equal">
+  <conditionalFormatting sqref="A1:O1 R1:Y1 AC1:AD1 R4:R30">
+    <cfRule type="cellIs" dxfId="21" priority="63" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E35:F35">
+    <cfRule type="duplicateValues" dxfId="20" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="27" priority="1495"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="duplicateValues" dxfId="26" priority="1517"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1521"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F30 F32:F1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="1488"/>
+  <conditionalFormatting sqref="F4:F30 F36:F1048576">
+    <cfRule type="duplicateValues" dxfId="17" priority="1492"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26 F28:F30">
-    <cfRule type="duplicateValues" dxfId="24" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27">
-    <cfRule type="duplicateValues" dxfId="23" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31">
-    <cfRule type="duplicateValues" dxfId="22" priority="6"/>
+  <conditionalFormatting sqref="F31:F34">
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F32:F1048576 F4:F25">
-    <cfRule type="duplicateValues" dxfId="21" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="1467"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q31">
-    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R31">
-    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+  <conditionalFormatting sqref="F36:F1048576 F4:F25">
+    <cfRule type="duplicateValues" dxfId="13" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1471"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y4:Y27">
-    <cfRule type="containsText" dxfId="10" priority="53" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="10" priority="57" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA25">
-    <cfRule type="duplicateValues" dxfId="9" priority="50"/>
-    <cfRule type="containsText" dxfId="8" priority="51" operator="containsText" text="null">
+    <cfRule type="duplicateValues" dxfId="9" priority="54"/>
+    <cfRule type="containsText" dxfId="8" priority="55" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",AA25)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="7" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="56"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -5503,15 +5973,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -5576,7 +6046,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5641,7 +6111,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -5724,30 +6194,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="64.84375" customWidth="1"/>
-    <col min="8" max="8" width="8.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.53515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.3828125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.3046875" customWidth="1"/>
-    <col min="14" max="14" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.3046875" customWidth="1"/>
-    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.69140625" customWidth="1"/>
-    <col min="18" max="18" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64.85546875" customWidth="1"/>
+    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" customWidth="1"/>
+    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.7109375" customWidth="1"/>
+    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -5806,7 +6276,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -5865,7 +6335,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21">
         <v>3</v>
       </c>
@@ -5924,7 +6394,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21">
         <v>4</v>
       </c>
@@ -5983,7 +6453,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21">
         <v>5</v>
       </c>
@@ -6042,7 +6512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21">
         <v>6</v>
       </c>
@@ -6101,7 +6571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21">
         <v>7</v>
       </c>
@@ -6160,7 +6630,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21">
         <v>8</v>
       </c>
@@ -6219,7 +6689,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21">
         <v>9</v>
       </c>
@@ -6278,7 +6748,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21">
         <v>10</v>
       </c>
@@ -6337,7 +6807,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21">
         <v>11</v>
       </c>
@@ -6396,7 +6866,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="21">
         <v>12</v>
       </c>
@@ -6455,7 +6925,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21">
         <v>13</v>
       </c>
@@ -6514,7 +6984,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21">
         <v>14</v>
       </c>
@@ -6583,15 +7053,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="27" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -6614,7 +7084,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>

--- a/Versão5/SIS/Ontologia_Luminotecnica.xlsx
+++ b/Versão5/SIS/Ontologia_Luminotecnica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F166689-03B6-426C-9124-DAE9B33F947A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7587C2-B9F4-4CA2-AB7A-994B26D1FEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="329">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -981,6 +981,84 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>De.Materialidade</t>
+  </si>
+  <si>
+    <t>Materialidades</t>
+  </si>
+  <si>
+    <t>Materiais</t>
+  </si>
+  <si>
+    <t>Mat.Cabo.de.Elétrica</t>
+  </si>
+  <si>
+    <t>Material usado em Cabo de Elétrica</t>
+  </si>
+  <si>
+    <t>Material utilizado en cables eléctricos</t>
+  </si>
+  <si>
+    <t>Material used in electrical cables</t>
+  </si>
+  <si>
+    <t>[ OST_Materials : OST_WireMaterials ]</t>
+  </si>
+  <si>
+    <t>[ IfcMaterial ]</t>
+  </si>
+  <si>
+    <t>[ 0M.20.20 ]</t>
+  </si>
+  <si>
+    <t>Mat.Calha.de.Elétrica</t>
+  </si>
+  <si>
+    <t>Material usado em Calha de Elétrica</t>
+  </si>
+  <si>
+    <t>Material utilizado en canaletas eléctricas</t>
+  </si>
+  <si>
+    <t>Material used in electrical gutters</t>
+  </si>
+  <si>
+    <t>Mat.Canaleta.de.Elétrica</t>
+  </si>
+  <si>
+    <t>Material usado em Canaleta de Elétrica</t>
+  </si>
+  <si>
+    <t>Material utilizado en conductos eléctricos</t>
+  </si>
+  <si>
+    <t>Material used in electrical conduits</t>
+  </si>
+  <si>
+    <t>Mat.Eletroduto.Flexível</t>
+  </si>
+  <si>
+    <t>Material usado em Eletroduto Flexível</t>
+  </si>
+  <si>
+    <t>Material utilizado en conductos eléctricos flexibles</t>
+  </si>
+  <si>
+    <t>Material used in flexible electrical conduits</t>
+  </si>
+  <si>
+    <t>Mat.Eletroduto.Rígido</t>
+  </si>
+  <si>
+    <t>Material usado em Eletroduto Rígido</t>
+  </si>
+  <si>
+    <t>Material utilizado en conductos eléctricos rígidos</t>
+  </si>
+  <si>
+    <t>Material used in rigid electrical conduits</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1531,11 +1609,17 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="28">
     <dxf>
       <font>
         <b val="0"/>
@@ -1627,6 +1711,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1738,11 +1830,53 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2185,14 +2319,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="33.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.69140625" customWidth="1"/>
+    <col min="2" max="2" width="33.69140625" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>46</v>
       </c>
@@ -2203,7 +2337,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>48</v>
       </c>
@@ -2214,7 +2348,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>50</v>
       </c>
@@ -2225,7 +2359,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>51</v>
       </c>
@@ -2236,7 +2370,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>52</v>
       </c>
@@ -2248,7 +2382,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>53</v>
       </c>
@@ -2260,7 +2394,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>54</v>
       </c>
@@ -2271,7 +2405,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="38" t="s">
         <v>56</v>
       </c>
@@ -2282,7 +2416,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>57</v>
       </c>
@@ -2293,7 +2427,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>59</v>
       </c>
@@ -2304,7 +2438,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
@@ -2315,7 +2449,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>62</v>
       </c>
@@ -2326,7 +2460,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
@@ -2337,7 +2471,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>64</v>
       </c>
@@ -2348,7 +2482,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>65</v>
       </c>
@@ -2359,7 +2493,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>66</v>
       </c>
@@ -2370,7 +2504,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
@@ -2381,19 +2515,19 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46268.700817824072</v>
+        <v>46270.887389467593</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>69</v>
       </c>
@@ -2404,7 +2538,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
@@ -2415,7 +2549,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>72</v>
       </c>
@@ -2426,7 +2560,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>73</v>
       </c>
@@ -2437,7 +2571,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>74</v>
       </c>
@@ -2448,7 +2582,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>88</v>
       </c>
@@ -2468,39 +2602,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AD35"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AD40"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="64" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.5703125" style="59" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="59" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="38.5703125" style="59" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="59" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.15234375" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.3046875" style="59" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.15234375" style="59" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3828125" style="64" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.53515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.15234375" style="59" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.3046875" style="59" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.15234375" style="59" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="38.53515625" style="59" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="39" style="59" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.42578125" style="59" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.15234375" style="59" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.15234375" style="59" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.69140625" style="59" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8" style="59" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16.85546875" style="65" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.3828125" style="59" customWidth="1"/>
+    <col min="26" max="26" width="6.84375" style="59" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.84375" style="65" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="59" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="2.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="59"/>
+    <col min="29" max="29" width="7.3046875" style="59" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="2.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.15234375" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="44" t="s">
         <v>154</v>
       </c>
@@ -2592,24 +2726,24 @@
         <v>302</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="56">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C2" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>256</v>
-      </c>
-      <c r="E2" s="43" t="s">
-        <v>257</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>254</v>
+      <c r="C2" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="F2" s="69" t="s">
+        <v>306</v>
       </c>
       <c r="G2" s="57" t="s">
         <v>9</v>
@@ -2627,88 +2761,89 @@
         <v>9</v>
       </c>
       <c r="L2" s="34" t="str">
-        <f t="shared" ref="L2:L30" si="0">CONCATENATE("", C2)</f>
-        <v>LuminoTécnicos</v>
+        <f t="shared" ref="L2:O6" si="0">SUBSTITUTE(CONCATENATE("", C2), ".", " ")</f>
+        <v>De Materialidade</v>
       </c>
       <c r="M2" s="34" t="str">
-        <f t="shared" ref="M2:M30" si="1">CONCATENATE("", D2)</f>
-        <v>Sistemas.Elétricos</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
       </c>
       <c r="N2" s="34" t="str">
-        <f t="shared" ref="N2:N30" si="2">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Sistemas de Iluminação</v>
-      </c>
-      <c r="O2" s="30" t="str">
-        <f t="shared" ref="O2:O3" si="3">IF(ISNUMBER(FIND("Ifc",F2)),CONCATENATE("Classe IFC:   ",F2),CONCATENATE("",F2))</f>
-        <v>Circuito.Luz.Geral</v>
-      </c>
-      <c r="P2" s="53" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q2" s="53" t="s">
-        <v>206</v>
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O2" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Mat Cabo de Elétrica</v>
+      </c>
+      <c r="P2" s="70" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q2" s="30" t="s">
+        <v>308</v>
       </c>
       <c r="R2" s="30" t="s">
-        <v>272</v>
+        <v>309</v>
       </c>
       <c r="S2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="30" t="s">
-        <v>258</v>
+      <c r="T2" s="30" t="str">
+        <f t="shared" ref="T2:V6" si="1">SUBSTITUTE(C2, ".", " ")</f>
+        <v>De Materialidade</v>
       </c>
       <c r="U2" s="30" t="str">
-        <f t="shared" ref="U2:U3" si="4">SUBSTITUTE(D2, "_", " ")</f>
-        <v>Sistemas.Elétricos</v>
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
       </c>
       <c r="V2" s="30" t="str">
-        <f t="shared" ref="V2:V3" si="5">SUBSTITUTE(E2, "_", " ")</f>
-        <v>Sistemas.de.Iluminação</v>
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
       </c>
       <c r="W2" s="30" t="s">
         <v>237</v>
       </c>
       <c r="X2" s="58" t="str">
-        <f t="shared" ref="X2:X35" si="6">CONCATENATE("Key-ILUM-",A2)</f>
+        <f t="shared" ref="X2:X6" si="2">CONCATENATE("Key-ILUM-",A2)</f>
         <v>Key-ILUM-2</v>
       </c>
-      <c r="Y2" s="61" t="s">
-        <v>208</v>
+      <c r="Y2" s="30" t="s">
+        <v>310</v>
       </c>
       <c r="Z2" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="61" t="s">
-        <v>209</v>
+      <c r="AA2" s="30" t="s">
+        <v>311</v>
       </c>
       <c r="AB2" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC2" s="30" t="s">
-        <v>259</v>
+        <v>312</v>
       </c>
       <c r="AD2" s="67" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="56">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C3" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>256</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>257</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>255</v>
+      <c r="C3" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="F3" s="69" t="s">
+        <v>313</v>
       </c>
       <c r="G3" s="57" t="s">
         <v>9</v>
@@ -2727,555 +2862,569 @@
       </c>
       <c r="L3" s="34" t="str">
         <f t="shared" si="0"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="M3" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N3" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O3" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Mat Calha de Elétrica</v>
+      </c>
+      <c r="P3" s="70" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="R3" s="30" t="s">
+        <v>316</v>
+      </c>
+      <c r="S3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U3" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V3" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W3" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X3" s="58" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-ILUM-3</v>
+      </c>
+      <c r="Y3" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="Z3" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB3" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD3" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="56">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="F4" s="69" t="s">
+        <v>317</v>
+      </c>
+      <c r="G4" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="M4" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N4" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O4" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Mat Canaleta de Elétrica</v>
+      </c>
+      <c r="P4" s="70" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q4" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="R4" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U4" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V4" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W4" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X4" s="58" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-ILUM-4</v>
+      </c>
+      <c r="Y4" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="Z4" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB4" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC4" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD4" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="56">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="F5" s="69" t="s">
+        <v>321</v>
+      </c>
+      <c r="G5" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="M5" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N5" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O5" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Mat Eletroduto Flexível</v>
+      </c>
+      <c r="P5" s="70" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q5" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="R5" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="S5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T5" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U5" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V5" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W5" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X5" s="58" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-ILUM-5</v>
+      </c>
+      <c r="Y5" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="Z5" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB5" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC5" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD5" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="56">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="F6" s="69" t="s">
+        <v>325</v>
+      </c>
+      <c r="G6" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="M6" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N6" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O6" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v>Mat Eletroduto Rígido</v>
+      </c>
+      <c r="P6" s="70" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q6" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="R6" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="S6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T6" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U6" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V6" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W6" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X6" s="58" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-ILUM-6</v>
+      </c>
+      <c r="Y6" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="Z6" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB6" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC6" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD6" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="56">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>257</v>
+      </c>
+      <c r="F7" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="G7" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="34" t="str">
+        <f t="shared" ref="L7:L35" si="3">CONCATENATE("", C7)</f>
         <v>LuminoTécnicos</v>
       </c>
-      <c r="M3" s="34" t="str">
-        <f t="shared" si="1"/>
+      <c r="M7" s="34" t="str">
+        <f t="shared" ref="M7:M35" si="4">CONCATENATE("", D7)</f>
         <v>Sistemas.Elétricos</v>
       </c>
-      <c r="N3" s="34" t="str">
-        <f t="shared" si="2"/>
+      <c r="N7" s="34" t="str">
+        <f t="shared" ref="N7:N35" si="5">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
         <v>Sistemas de Iluminação</v>
       </c>
-      <c r="O3" s="30" t="str">
+      <c r="O7" s="30" t="str">
+        <f t="shared" ref="O7:O8" si="6">IF(ISNUMBER(FIND("Ifc",F7)),CONCATENATE("Classe IFC:   ",F7),CONCATENATE("",F7))</f>
+        <v>Circuito.Luz.Geral</v>
+      </c>
+      <c r="P7" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q7" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="R7" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T7" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="U7" s="30" t="str">
+        <f t="shared" ref="U7:U8" si="7">SUBSTITUTE(D7, "_", " ")</f>
+        <v>Sistemas.Elétricos</v>
+      </c>
+      <c r="V7" s="30" t="str">
+        <f t="shared" ref="V7:V8" si="8">SUBSTITUTE(E7, "_", " ")</f>
+        <v>Sistemas.de.Iluminação</v>
+      </c>
+      <c r="W7" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X7" s="58" t="str">
+        <f t="shared" ref="X7:X40" si="9">CONCATENATE("Key-ILUM-",A7)</f>
+        <v>Key-ILUM-7</v>
+      </c>
+      <c r="Y7" s="61" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z7" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB7" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC7" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="AD7" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="56">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>257</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="G8" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="34" t="str">
         <f t="shared" si="3"/>
-        <v>Circuito.Luz.Emergência</v>
-      </c>
-      <c r="P3" s="53" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q3" s="53" t="s">
-        <v>206</v>
-      </c>
-      <c r="R3" s="30" t="s">
-        <v>272</v>
-      </c>
-      <c r="S3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T3" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="U3" s="30" t="str">
+        <v>LuminoTécnicos</v>
+      </c>
+      <c r="M8" s="34" t="str">
         <f t="shared" si="4"/>
         <v>Sistemas.Elétricos</v>
       </c>
-      <c r="V3" s="30" t="str">
+      <c r="N8" s="34" t="str">
         <f t="shared" si="5"/>
+        <v>Sistemas de Iluminação</v>
+      </c>
+      <c r="O8" s="30" t="str">
+        <f t="shared" si="6"/>
+        <v>Circuito.Luz.Emergência</v>
+      </c>
+      <c r="P8" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q8" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="R8" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="S8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="U8" s="30" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistemas.Elétricos</v>
+      </c>
+      <c r="V8" s="30" t="str">
+        <f t="shared" si="8"/>
         <v>Sistemas.de.Iluminação</v>
-      </c>
-      <c r="W3" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="X3" s="58" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-ILUM-3</v>
-      </c>
-      <c r="Y3" s="61" t="s">
-        <v>208</v>
-      </c>
-      <c r="Z3" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA3" s="61" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB3" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC3" s="30" t="s">
-        <v>259</v>
-      </c>
-      <c r="AD3" s="67" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="56">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="62" t="s">
-        <v>96</v>
-      </c>
-      <c r="G4" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M4" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N4" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>Luminária</v>
-      </c>
-      <c r="O4" s="30" t="str">
-        <f t="shared" ref="O4:O30" si="7">IF(ISNUMBER(FIND("Ifc",F4)),CONCATENATE("Classe IFC:   ",F4),CONCATENATE("",F4))</f>
-        <v>Luz.Aletas</v>
-      </c>
-      <c r="P4" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q4" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="R4" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="S4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T4" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="U4" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="V4" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="W4" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="X4" s="58" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-ILUM-4</v>
-      </c>
-      <c r="Y4" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="Z4" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA4" s="61" t="s">
-        <v>264</v>
-      </c>
-      <c r="AB4" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC4" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="AD4" s="67" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="56">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="62" t="s">
-        <v>98</v>
-      </c>
-      <c r="G5" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="L5" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M5" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N5" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>Luminária</v>
-      </c>
-      <c r="O5" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">Luz.Antiofuscamento </v>
-      </c>
-      <c r="P5" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q5" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="R5" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="S5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T5" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="U5" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="V5" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="W5" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="X5" s="58" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-ILUM-5</v>
-      </c>
-      <c r="Y5" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="Z5" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA5" s="61" t="s">
-        <v>264</v>
-      </c>
-      <c r="AB5" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC5" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="AD5" s="67" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="56">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="G6" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M6" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N6" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>Luminária</v>
-      </c>
-      <c r="O6" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Arandela</v>
-      </c>
-      <c r="P6" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q6" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="R6" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="S6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T6" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="U6" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="V6" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="W6" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="X6" s="58" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-ILUM-6</v>
-      </c>
-      <c r="Y6" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="Z6" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA6" s="61" t="s">
-        <v>264</v>
-      </c>
-      <c r="AB6" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC6" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="AD6" s="67" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="56">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="62" t="s">
-        <v>95</v>
-      </c>
-      <c r="G7" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M7" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N7" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>Luminária</v>
-      </c>
-      <c r="O7" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Baliza</v>
-      </c>
-      <c r="P7" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q7" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="R7" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="S7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T7" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="U7" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="V7" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="W7" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="X7" s="58" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-ILUM-7</v>
-      </c>
-      <c r="Y7" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="Z7" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA7" s="61" t="s">
-        <v>264</v>
-      </c>
-      <c r="AB7" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC7" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="AD7" s="67" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="56">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E8" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="62" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>LuminoTécnicos</v>
-      </c>
-      <c r="M8" s="34" t="str">
-        <f t="shared" si="1"/>
-        <v>Elemento.Iluminação</v>
-      </c>
-      <c r="N8" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>Luminária</v>
-      </c>
-      <c r="O8" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Difusa</v>
-      </c>
-      <c r="P8" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q8" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="R8" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="S8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T8" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="U8" s="30" t="s">
-        <v>184</v>
-      </c>
-      <c r="V8" s="30" t="s">
-        <v>238</v>
       </c>
       <c r="W8" s="30" t="s">
         <v>237</v>
       </c>
       <c r="X8" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-8</v>
       </c>
-      <c r="Y8" s="30" t="s">
-        <v>239</v>
+      <c r="Y8" s="61" t="s">
+        <v>208</v>
       </c>
       <c r="Z8" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AA8" s="61" t="s">
-        <v>264</v>
+        <v>209</v>
       </c>
       <c r="AB8" s="67" t="s">
         <v>9</v>
       </c>
       <c r="AC8" s="30" t="s">
-        <v>183</v>
+        <v>259</v>
       </c>
       <c r="AD8" s="67" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="56">
         <v>9</v>
       </c>
@@ -3292,7 +3441,7 @@
         <v>45</v>
       </c>
       <c r="F9" s="62" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G9" s="63" t="s">
         <v>9</v>
@@ -3310,29 +3459,29 @@
         <v>9</v>
       </c>
       <c r="L9" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M9" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N9" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O9" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Embutida.Fixa</v>
+        <f t="shared" ref="O9:O35" si="10">IF(ISNUMBER(FIND("Ifc",F9)),CONCATENATE("Classe IFC:   ",F9),CONCATENATE("",F9))</f>
+        <v>Luz.Aletas</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="S9" s="30" t="s">
         <v>9</v>
@@ -3350,7 +3499,7 @@
         <v>237</v>
       </c>
       <c r="X9" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-9</v>
       </c>
       <c r="Y9" s="30" t="s">
@@ -3372,7 +3521,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="56">
         <v>10</v>
       </c>
@@ -3389,7 +3538,7 @@
         <v>45</v>
       </c>
       <c r="F10" s="62" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G10" s="63" t="s">
         <v>9</v>
@@ -3407,29 +3556,29 @@
         <v>9</v>
       </c>
       <c r="L10" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M10" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N10" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O10" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Embutida.Orientável</v>
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">Luz.Antiofuscamento </v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="Q10" s="30" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="R10" s="30" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="S10" s="30" t="s">
         <v>9</v>
@@ -3447,7 +3596,7 @@
         <v>237</v>
       </c>
       <c r="X10" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-10</v>
       </c>
       <c r="Y10" s="30" t="s">
@@ -3469,7 +3618,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="56">
         <v>11</v>
       </c>
@@ -3486,7 +3635,7 @@
         <v>45</v>
       </c>
       <c r="F11" s="62" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="G11" s="63" t="s">
         <v>9</v>
@@ -3504,29 +3653,29 @@
         <v>9</v>
       </c>
       <c r="L11" s="34" t="str">
-        <f t="shared" ref="L11" si="8">CONCATENATE("", C11)</f>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M11" s="34" t="str">
-        <f t="shared" ref="M11" si="9">CONCATENATE("", D11)</f>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N11" s="34" t="str">
-        <f t="shared" ref="N11" si="10">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O11" s="30" t="str">
-        <f t="shared" ref="O11" si="11">IF(ISNUMBER(FIND("Ifc",F11)),CONCATENATE("Classe IFC:   ",F11),CONCATENATE("",F11))</f>
-        <v>Luz.Externa</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Arandela</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>252</v>
+        <v>116</v>
       </c>
       <c r="Q11" s="30" t="s">
-        <v>253</v>
+        <v>146</v>
       </c>
       <c r="R11" s="30" t="s">
-        <v>251</v>
+        <v>159</v>
       </c>
       <c r="S11" s="30" t="s">
         <v>9</v>
@@ -3544,7 +3693,7 @@
         <v>237</v>
       </c>
       <c r="X11" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-11</v>
       </c>
       <c r="Y11" s="30" t="s">
@@ -3566,7 +3715,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="56">
         <v>12</v>
       </c>
@@ -3583,7 +3732,7 @@
         <v>45</v>
       </c>
       <c r="F12" s="62" t="s">
-        <v>247</v>
+        <v>95</v>
       </c>
       <c r="G12" s="63" t="s">
         <v>9</v>
@@ -3601,29 +3750,29 @@
         <v>9</v>
       </c>
       <c r="L12" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M12" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N12" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O12" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Externa.Urbana</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Baliza</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>249</v>
+        <v>117</v>
       </c>
       <c r="Q12" s="30" t="s">
-        <v>248</v>
+        <v>147</v>
       </c>
       <c r="R12" s="30" t="s">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="S12" s="30" t="s">
         <v>9</v>
@@ -3641,7 +3790,7 @@
         <v>237</v>
       </c>
       <c r="X12" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-12</v>
       </c>
       <c r="Y12" s="30" t="s">
@@ -3663,7 +3812,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="56">
         <v>13</v>
       </c>
@@ -3680,7 +3829,7 @@
         <v>45</v>
       </c>
       <c r="F13" s="62" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="G13" s="63" t="s">
         <v>9</v>
@@ -3698,29 +3847,29 @@
         <v>9</v>
       </c>
       <c r="L13" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M13" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N13" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O13" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Feixe.Amplo</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Difusa</v>
       </c>
       <c r="P13" s="30" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q13" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R13" s="30" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="S13" s="30" t="s">
         <v>9</v>
@@ -3738,7 +3887,7 @@
         <v>237</v>
       </c>
       <c r="X13" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-13</v>
       </c>
       <c r="Y13" s="30" t="s">
@@ -3760,7 +3909,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="56">
         <v>14</v>
       </c>
@@ -3777,7 +3926,7 @@
         <v>45</v>
       </c>
       <c r="F14" s="62" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G14" s="63" t="s">
         <v>9</v>
@@ -3795,29 +3944,29 @@
         <v>9</v>
       </c>
       <c r="L14" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M14" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N14" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O14" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Gôndola</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Embutida.Fixa</v>
       </c>
       <c r="P14" s="30" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="Q14" s="30" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="R14" s="30" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="S14" s="30" t="s">
         <v>9</v>
@@ -3835,7 +3984,7 @@
         <v>237</v>
       </c>
       <c r="X14" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-14</v>
       </c>
       <c r="Y14" s="30" t="s">
@@ -3857,7 +4006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="56">
         <v>15</v>
       </c>
@@ -3874,7 +4023,7 @@
         <v>45</v>
       </c>
       <c r="F15" s="62" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G15" s="63" t="s">
         <v>9</v>
@@ -3892,29 +4041,29 @@
         <v>9</v>
       </c>
       <c r="L15" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M15" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N15" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O15" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Grande.Altura</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Embutida.Orientável</v>
       </c>
       <c r="P15" s="30" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="Q15" s="30" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="R15" s="30" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S15" s="30" t="s">
         <v>9</v>
@@ -3932,7 +4081,7 @@
         <v>237</v>
       </c>
       <c r="X15" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-15</v>
       </c>
       <c r="Y15" s="30" t="s">
@@ -3954,7 +4103,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="56">
         <v>16</v>
       </c>
@@ -3971,7 +4120,7 @@
         <v>45</v>
       </c>
       <c r="F16" s="62" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G16" s="63" t="s">
         <v>9</v>
@@ -3989,29 +4138,29 @@
         <v>9</v>
       </c>
       <c r="L16" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L16" si="11">CONCATENATE("", C16)</f>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M16" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="M16" si="12">CONCATENATE("", D16)</f>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N16" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="N16" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E16),"."," ")," De "," de "))</f>
         <v>Luminária</v>
       </c>
       <c r="O16" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Hermética</v>
+        <f t="shared" ref="O16" si="14">IF(ISNUMBER(FIND("Ifc",F16)),CONCATENATE("Classe IFC:   ",F16),CONCATENATE("",F16))</f>
+        <v>Luz.Externa</v>
       </c>
       <c r="P16" s="30" t="s">
-        <v>124</v>
+        <v>252</v>
       </c>
       <c r="Q16" s="30" t="s">
-        <v>145</v>
+        <v>253</v>
       </c>
       <c r="R16" s="30" t="s">
-        <v>166</v>
+        <v>251</v>
       </c>
       <c r="S16" s="30" t="s">
         <v>9</v>
@@ -4029,7 +4178,7 @@
         <v>237</v>
       </c>
       <c r="X16" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-16</v>
       </c>
       <c r="Y16" s="30" t="s">
@@ -4051,7 +4200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="56">
         <v>17</v>
       </c>
@@ -4068,7 +4217,7 @@
         <v>45</v>
       </c>
       <c r="F17" s="62" t="s">
-        <v>113</v>
+        <v>247</v>
       </c>
       <c r="G17" s="63" t="s">
         <v>9</v>
@@ -4086,29 +4235,29 @@
         <v>9</v>
       </c>
       <c r="L17" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M17" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N17" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O17" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.LEDFita</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Externa.Urbana</v>
       </c>
       <c r="P17" s="30" t="s">
-        <v>125</v>
+        <v>249</v>
       </c>
       <c r="Q17" s="30" t="s">
-        <v>137</v>
+        <v>248</v>
       </c>
       <c r="R17" s="30" t="s">
-        <v>167</v>
+        <v>250</v>
       </c>
       <c r="S17" s="30" t="s">
         <v>9</v>
@@ -4126,7 +4275,7 @@
         <v>237</v>
       </c>
       <c r="X17" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-17</v>
       </c>
       <c r="Y17" s="30" t="s">
@@ -4136,7 +4285,7 @@
         <v>9</v>
       </c>
       <c r="AA17" s="61" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AB17" s="67" t="s">
         <v>9</v>
@@ -4148,7 +4297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="56">
         <v>18</v>
       </c>
@@ -4165,7 +4314,7 @@
         <v>45</v>
       </c>
       <c r="F18" s="62" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G18" s="63" t="s">
         <v>9</v>
@@ -4183,29 +4332,29 @@
         <v>9</v>
       </c>
       <c r="L18" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M18" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N18" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O18" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.LEDTubular</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Feixe.Amplo</v>
       </c>
       <c r="P18" s="30" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="Q18" s="30" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="R18" s="30" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="S18" s="30" t="s">
         <v>9</v>
@@ -4223,7 +4372,7 @@
         <v>237</v>
       </c>
       <c r="X18" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-18</v>
       </c>
       <c r="Y18" s="30" t="s">
@@ -4233,7 +4382,7 @@
         <v>9</v>
       </c>
       <c r="AA18" s="61" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AB18" s="67" t="s">
         <v>9</v>
@@ -4245,7 +4394,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="56">
         <v>19</v>
       </c>
@@ -4262,7 +4411,7 @@
         <v>45</v>
       </c>
       <c r="F19" s="62" t="s">
-        <v>241</v>
+        <v>105</v>
       </c>
       <c r="G19" s="63" t="s">
         <v>9</v>
@@ -4280,29 +4429,29 @@
         <v>9</v>
       </c>
       <c r="L19" s="34" t="str">
-        <f t="shared" ref="L19" si="12">CONCATENATE("", C19)</f>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M19" s="34" t="str">
-        <f t="shared" ref="M19" si="13">CONCATENATE("", D19)</f>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N19" s="34" t="str">
-        <f t="shared" ref="N19" si="14">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E19),"."," ")," De "," de "))</f>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O19" s="30" t="str">
-        <f t="shared" ref="O19" si="15">IF(ISNUMBER(FIND("Ifc",F19)),CONCATENATE("Classe IFC:   ",F19),CONCATENATE("",F19))</f>
-        <v>Luz.TuboFluorescente</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Gôndola</v>
       </c>
       <c r="P19" s="30" t="s">
-        <v>242</v>
+        <v>122</v>
       </c>
       <c r="Q19" s="30" t="s">
-        <v>243</v>
+        <v>152</v>
       </c>
       <c r="R19" s="30" t="s">
-        <v>244</v>
+        <v>164</v>
       </c>
       <c r="S19" s="30" t="s">
         <v>9</v>
@@ -4320,7 +4469,7 @@
         <v>237</v>
       </c>
       <c r="X19" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-19</v>
       </c>
       <c r="Y19" s="30" t="s">
@@ -4342,7 +4491,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="56">
         <v>20</v>
       </c>
@@ -4359,7 +4508,7 @@
         <v>45</v>
       </c>
       <c r="F20" s="62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G20" s="63" t="s">
         <v>9</v>
@@ -4377,29 +4526,29 @@
         <v>9</v>
       </c>
       <c r="L20" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M20" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N20" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O20" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Linear</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Grande.Altura</v>
       </c>
       <c r="P20" s="30" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="Q20" s="30" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="R20" s="30" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="S20" s="30" t="s">
         <v>9</v>
@@ -4417,7 +4566,7 @@
         <v>237</v>
       </c>
       <c r="X20" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-20</v>
       </c>
       <c r="Y20" s="30" t="s">
@@ -4439,7 +4588,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="56">
         <v>21</v>
       </c>
@@ -4456,7 +4605,7 @@
         <v>45</v>
       </c>
       <c r="F21" s="62" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G21" s="63" t="s">
         <v>9</v>
@@ -4474,29 +4623,29 @@
         <v>9</v>
       </c>
       <c r="L21" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M21" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N21" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O21" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Painel</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Hermética</v>
       </c>
       <c r="P21" s="30" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Q21" s="30" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="R21" s="30" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="S21" s="30" t="s">
         <v>9</v>
@@ -4514,7 +4663,7 @@
         <v>237</v>
       </c>
       <c r="X21" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-21</v>
       </c>
       <c r="Y21" s="30" t="s">
@@ -4536,7 +4685,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="56">
         <v>22</v>
       </c>
@@ -4553,7 +4702,7 @@
         <v>45</v>
       </c>
       <c r="F22" s="62" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G22" s="63" t="s">
         <v>9</v>
@@ -4571,29 +4720,29 @@
         <v>9</v>
       </c>
       <c r="L22" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M22" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N22" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O22" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Pendente</v>
+        <f t="shared" si="10"/>
+        <v>Luz.LEDFita</v>
       </c>
       <c r="P22" s="30" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Q22" s="30" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="R22" s="30" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="S22" s="30" t="s">
         <v>9</v>
@@ -4611,7 +4760,7 @@
         <v>237</v>
       </c>
       <c r="X22" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-22</v>
       </c>
       <c r="Y22" s="30" t="s">
@@ -4621,7 +4770,7 @@
         <v>9</v>
       </c>
       <c r="AA22" s="61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AB22" s="67" t="s">
         <v>9</v>
@@ -4633,7 +4782,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="56">
         <v>23</v>
       </c>
@@ -4650,7 +4799,7 @@
         <v>45</v>
       </c>
       <c r="F23" s="62" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G23" s="63" t="s">
         <v>9</v>
@@ -4668,29 +4817,29 @@
         <v>9</v>
       </c>
       <c r="L23" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M23" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N23" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O23" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Plafon</v>
+        <f t="shared" si="10"/>
+        <v>Luz.LEDTubular</v>
       </c>
       <c r="P23" s="30" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="Q23" s="30" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="R23" s="30" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="S23" s="30" t="s">
         <v>9</v>
@@ -4708,7 +4857,7 @@
         <v>237</v>
       </c>
       <c r="X23" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-23</v>
       </c>
       <c r="Y23" s="30" t="s">
@@ -4718,7 +4867,7 @@
         <v>9</v>
       </c>
       <c r="AA23" s="61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AB23" s="67" t="s">
         <v>9</v>
@@ -4730,7 +4879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="56">
         <v>24</v>
       </c>
@@ -4747,7 +4896,7 @@
         <v>45</v>
       </c>
       <c r="F24" s="62" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G24" s="63" t="s">
         <v>9</v>
@@ -4765,29 +4914,29 @@
         <v>9</v>
       </c>
       <c r="L24" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L24" si="15">CONCATENATE("", C24)</f>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M24" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="M24" si="16">CONCATENATE("", D24)</f>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N24" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="N24" si="17">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E24),"."," ")," De "," de "))</f>
         <v>Luminária</v>
       </c>
       <c r="O24" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Sensorizada</v>
+        <f t="shared" ref="O24" si="18">IF(ISNUMBER(FIND("Ifc",F24)),CONCATENATE("Classe IFC:   ",F24),CONCATENATE("",F24))</f>
+        <v>Luz.TuboFluorescente</v>
       </c>
       <c r="P24" s="30" t="s">
-        <v>131</v>
+        <v>242</v>
       </c>
       <c r="Q24" s="30" t="s">
-        <v>142</v>
+        <v>243</v>
       </c>
       <c r="R24" s="30" t="s">
-        <v>172</v>
+        <v>244</v>
       </c>
       <c r="S24" s="30" t="s">
         <v>9</v>
@@ -4805,7 +4954,7 @@
         <v>237</v>
       </c>
       <c r="X24" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-24</v>
       </c>
       <c r="Y24" s="30" t="s">
@@ -4827,7 +4976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="56">
         <v>25</v>
       </c>
@@ -4844,7 +4993,7 @@
         <v>45</v>
       </c>
       <c r="F25" s="62" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G25" s="63" t="s">
         <v>9</v>
@@ -4862,29 +5011,29 @@
         <v>9</v>
       </c>
       <c r="L25" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M25" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N25" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O25" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Spot</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Linear</v>
       </c>
       <c r="P25" s="30" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="Q25" s="30" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="R25" s="30" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="S25" s="30" t="s">
         <v>9</v>
@@ -4902,7 +5051,7 @@
         <v>237</v>
       </c>
       <c r="X25" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-25</v>
       </c>
       <c r="Y25" s="30" t="s">
@@ -4912,7 +5061,7 @@
         <v>9</v>
       </c>
       <c r="AA25" s="61" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AB25" s="67" t="s">
         <v>9</v>
@@ -4924,7 +5073,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="56">
         <v>26</v>
       </c>
@@ -4941,7 +5090,7 @@
         <v>45</v>
       </c>
       <c r="F26" s="62" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G26" s="63" t="s">
         <v>9</v>
@@ -4959,29 +5108,29 @@
         <v>9</v>
       </c>
       <c r="L26" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M26" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N26" s="34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>Luminária</v>
       </c>
       <c r="O26" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Luz.Trilho</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Painel</v>
       </c>
       <c r="P26" s="30" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="Q26" s="30" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="R26" s="30" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="S26" s="30" t="s">
         <v>9</v>
@@ -4999,7 +5148,7 @@
         <v>237</v>
       </c>
       <c r="X26" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-26</v>
       </c>
       <c r="Y26" s="30" t="s">
@@ -5021,7 +5170,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="56">
         <v>27</v>
       </c>
@@ -5035,10 +5184,10 @@
         <v>233</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="F27" s="62" t="s">
-        <v>240</v>
+        <v>106</v>
       </c>
       <c r="G27" s="63" t="s">
         <v>9</v>
@@ -5056,29 +5205,29 @@
         <v>9</v>
       </c>
       <c r="L27" s="34" t="str">
-        <f t="shared" ref="L27" si="16">CONCATENATE("", C27)</f>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M27" s="34" t="str">
-        <f t="shared" ref="M27" si="17">CONCATENATE("", D27)</f>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N27" s="34" t="str">
-        <f t="shared" ref="N27" si="18">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E27),"."," ")," De "," de "))</f>
-        <v>Acessórios de Iluminação</v>
+        <f t="shared" si="5"/>
+        <v>Luminária</v>
       </c>
       <c r="O27" s="30" t="str">
-        <f t="shared" ref="O27" si="19">IF(ISNUMBER(FIND("Ifc",F27)),CONCATENATE("Classe IFC:   ",F27),CONCATENATE("",F27))</f>
-        <v>Acessório.Luz</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Pendente</v>
       </c>
       <c r="P27" s="30" t="s">
-        <v>235</v>
+        <v>129</v>
       </c>
       <c r="Q27" s="30" t="s">
-        <v>236</v>
+        <v>140</v>
       </c>
       <c r="R27" s="30" t="s">
-        <v>245</v>
+        <v>176</v>
       </c>
       <c r="S27" s="30" t="s">
         <v>9</v>
@@ -5096,7 +5245,7 @@
         <v>237</v>
       </c>
       <c r="X27" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-27</v>
       </c>
       <c r="Y27" s="30" t="s">
@@ -5106,7 +5255,7 @@
         <v>9</v>
       </c>
       <c r="AA27" s="61" t="s">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="AB27" s="67" t="s">
         <v>9</v>
@@ -5118,7 +5267,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="56">
         <v>28</v>
       </c>
@@ -5132,10 +5281,10 @@
         <v>233</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>234</v>
+        <v>45</v>
       </c>
       <c r="F28" s="62" t="s">
-        <v>186</v>
+        <v>107</v>
       </c>
       <c r="G28" s="63" t="s">
         <v>9</v>
@@ -5153,29 +5302,29 @@
         <v>9</v>
       </c>
       <c r="L28" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M28" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N28" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>Analítico de Luz</v>
+        <f t="shared" si="5"/>
+        <v>Luminária</v>
       </c>
       <c r="O28" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Ponto.Iluminado</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Plafon</v>
       </c>
       <c r="P28" s="30" t="s">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="Q28" s="30" t="s">
-        <v>191</v>
+        <v>141</v>
       </c>
       <c r="R28" s="30" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="S28" s="30" t="s">
         <v>9</v>
@@ -5184,38 +5333,38 @@
         <v>44</v>
       </c>
       <c r="U28" s="30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="V28" s="30" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="W28" s="30" t="s">
         <v>237</v>
       </c>
       <c r="X28" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-28</v>
       </c>
-      <c r="Y28" s="67" t="s">
-        <v>9</v>
+      <c r="Y28" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z28" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="AA28" s="67" t="s">
-        <v>9</v>
+      <c r="AA28" s="61" t="s">
+        <v>264</v>
       </c>
       <c r="AB28" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="AC28" s="67" t="s">
-        <v>9</v>
+      <c r="AC28" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="AD28" s="67" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="56">
         <v>29</v>
       </c>
@@ -5229,10 +5378,10 @@
         <v>233</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>234</v>
+        <v>45</v>
       </c>
       <c r="F29" s="62" t="s">
-        <v>187</v>
+        <v>246</v>
       </c>
       <c r="G29" s="63" t="s">
         <v>9</v>
@@ -5250,29 +5399,29 @@
         <v>9</v>
       </c>
       <c r="L29" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M29" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N29" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>Analítico de Luz</v>
+        <f t="shared" si="5"/>
+        <v>Luminária</v>
       </c>
       <c r="O29" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Linha.Iluminada</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Sensorizada</v>
       </c>
       <c r="P29" s="30" t="s">
-        <v>193</v>
+        <v>131</v>
       </c>
       <c r="Q29" s="30" t="s">
-        <v>192</v>
+        <v>142</v>
       </c>
       <c r="R29" s="30" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="S29" s="30" t="s">
         <v>9</v>
@@ -5281,38 +5430,38 @@
         <v>44</v>
       </c>
       <c r="U29" s="30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="V29" s="30" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="W29" s="30" t="s">
         <v>237</v>
       </c>
       <c r="X29" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-29</v>
       </c>
-      <c r="Y29" s="67" t="s">
-        <v>9</v>
+      <c r="Y29" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z29" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="AA29" s="67" t="s">
-        <v>9</v>
+      <c r="AA29" s="61" t="s">
+        <v>264</v>
       </c>
       <c r="AB29" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="AC29" s="67" t="s">
-        <v>9</v>
+      <c r="AC29" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="AD29" s="67" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="56">
         <v>30</v>
       </c>
@@ -5326,10 +5475,10 @@
         <v>233</v>
       </c>
       <c r="E30" s="43" t="s">
-        <v>234</v>
+        <v>45</v>
       </c>
       <c r="F30" s="62" t="s">
-        <v>188</v>
+        <v>108</v>
       </c>
       <c r="G30" s="63" t="s">
         <v>9</v>
@@ -5347,29 +5496,29 @@
         <v>9</v>
       </c>
       <c r="L30" s="34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>LuminoTécnicos</v>
       </c>
       <c r="M30" s="34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>Elemento.Iluminação</v>
       </c>
       <c r="N30" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v>Analítico de Luz</v>
+        <f t="shared" si="5"/>
+        <v>Luminária</v>
       </c>
       <c r="O30" s="30" t="str">
-        <f t="shared" si="7"/>
-        <v>Area.Iluminada</v>
+        <f t="shared" si="10"/>
+        <v>Luz.Spot</v>
       </c>
       <c r="P30" s="30" t="s">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="Q30" s="30" t="s">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="R30" s="30" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="S30" s="30" t="s">
         <v>9</v>
@@ -5378,57 +5527,57 @@
         <v>44</v>
       </c>
       <c r="U30" s="30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="V30" s="30" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="W30" s="30" t="s">
         <v>237</v>
       </c>
       <c r="X30" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-30</v>
       </c>
-      <c r="Y30" s="67" t="s">
-        <v>9</v>
+      <c r="Y30" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z30" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="AA30" s="67" t="s">
-        <v>9</v>
+      <c r="AA30" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="AB30" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="AC30" s="67" t="s">
-        <v>9</v>
+      <c r="AC30" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="AD30" s="67" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="56">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C31" s="62" t="s">
-        <v>278</v>
-      </c>
-      <c r="D31" s="62" t="s">
-        <v>280</v>
-      </c>
-      <c r="E31" s="62" t="s">
-        <v>279</v>
+        <v>262</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>45</v>
       </c>
       <c r="F31" s="62" t="s">
-        <v>281</v>
-      </c>
-      <c r="G31" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="63" t="s">
         <v>9</v>
       </c>
       <c r="H31" s="57" t="s">
@@ -5444,91 +5593,88 @@
         <v>9</v>
       </c>
       <c r="L31" s="34" t="str">
-        <f t="shared" ref="L31:O35" si="20">SUBSTITUTE(CONCATENATE("", C31), ".", " ")</f>
-        <v>De API</v>
+        <f t="shared" si="3"/>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M31" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Macros</v>
+        <f t="shared" si="4"/>
+        <v>Elemento.Iluminação</v>
       </c>
       <c r="N31" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O31" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Função Auxiliar</v>
+        <f t="shared" si="5"/>
+        <v>Luminária</v>
+      </c>
+      <c r="O31" s="30" t="str">
+        <f t="shared" si="10"/>
+        <v>Luz.Trilho</v>
       </c>
       <c r="P31" s="30" t="s">
-        <v>282</v>
+        <v>133</v>
       </c>
       <c r="Q31" s="30" t="s">
-        <v>283</v>
+        <v>144</v>
       </c>
       <c r="R31" s="30" t="s">
-        <v>284</v>
+        <v>174</v>
       </c>
       <c r="S31" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="T31" s="30" t="str">
-        <f t="shared" ref="T31:V35" si="21">SUBSTITUTE(C31, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U31" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>Macros</v>
-      </c>
-      <c r="V31" s="66" t="str">
-        <f t="shared" si="21"/>
-        <v>Métodos</v>
+      <c r="T31" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="U31" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="V31" s="30" t="s">
+        <v>238</v>
       </c>
       <c r="W31" s="30" t="s">
         <v>237</v>
       </c>
       <c r="X31" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-31</v>
       </c>
-      <c r="Y31" s="67" t="s">
-        <v>9</v>
+      <c r="Y31" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z31" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="AA31" s="67" t="s">
-        <v>9</v>
+      <c r="AA31" s="61" t="s">
+        <v>264</v>
       </c>
       <c r="AB31" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="AC31" s="67" t="s">
-        <v>9</v>
+      <c r="AC31" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="AD31" s="67" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="56">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C32" s="62" t="s">
-        <v>278</v>
-      </c>
-      <c r="D32" s="62" t="s">
-        <v>280</v>
-      </c>
-      <c r="E32" s="62" t="s">
-        <v>279</v>
+        <v>262</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E32" s="43" t="s">
+        <v>210</v>
       </c>
       <c r="F32" s="62" t="s">
-        <v>285</v>
-      </c>
-      <c r="G32" s="57" t="s">
+        <v>240</v>
+      </c>
+      <c r="G32" s="63" t="s">
         <v>9</v>
       </c>
       <c r="H32" s="57" t="s">
@@ -5544,91 +5690,88 @@
         <v>9</v>
       </c>
       <c r="L32" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>De API</v>
+        <f t="shared" ref="L32" si="19">CONCATENATE("", C32)</f>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M32" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Macros</v>
+        <f t="shared" ref="M32" si="20">CONCATENATE("", D32)</f>
+        <v>Elemento.Iluminação</v>
       </c>
       <c r="N32" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O32" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Função Global</v>
+        <f t="shared" ref="N32" si="21">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E32),"."," ")," De "," de "))</f>
+        <v>Acessórios de Iluminação</v>
+      </c>
+      <c r="O32" s="30" t="str">
+        <f t="shared" ref="O32" si="22">IF(ISNUMBER(FIND("Ifc",F32)),CONCATENATE("Classe IFC:   ",F32),CONCATENATE("",F32))</f>
+        <v>Acessório.Luz</v>
       </c>
       <c r="P32" s="30" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
       <c r="Q32" s="30" t="s">
-        <v>287</v>
+        <v>236</v>
       </c>
       <c r="R32" s="30" t="s">
-        <v>288</v>
+        <v>245</v>
       </c>
       <c r="S32" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="T32" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>De API</v>
-      </c>
-      <c r="U32" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>Macros</v>
-      </c>
-      <c r="V32" s="66" t="str">
-        <f t="shared" si="21"/>
-        <v>Métodos</v>
+      <c r="T32" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="U32" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="V32" s="30" t="s">
+        <v>238</v>
       </c>
       <c r="W32" s="30" t="s">
         <v>237</v>
       </c>
       <c r="X32" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-32</v>
       </c>
-      <c r="Y32" s="67" t="s">
-        <v>9</v>
+      <c r="Y32" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="Z32" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="AA32" s="67" t="s">
-        <v>9</v>
+      <c r="AA32" s="61" t="s">
+        <v>232</v>
       </c>
       <c r="AB32" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="AC32" s="67" t="s">
-        <v>9</v>
+      <c r="AC32" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="AD32" s="67" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="56">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C33" s="62" t="s">
-        <v>278</v>
-      </c>
-      <c r="D33" s="62" t="s">
-        <v>280</v>
-      </c>
-      <c r="E33" s="62" t="s">
-        <v>279</v>
+        <v>262</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E33" s="43" t="s">
+        <v>234</v>
       </c>
       <c r="F33" s="62" t="s">
-        <v>289</v>
-      </c>
-      <c r="G33" s="57" t="s">
+        <v>186</v>
+      </c>
+      <c r="G33" s="63" t="s">
         <v>9</v>
       </c>
       <c r="H33" s="57" t="s">
@@ -5644,50 +5787,47 @@
         <v>9</v>
       </c>
       <c r="L33" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>De API</v>
+        <f t="shared" si="3"/>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M33" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Macros</v>
+        <f t="shared" si="4"/>
+        <v>Elemento.Iluminação</v>
       </c>
       <c r="N33" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O33" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Função Local</v>
+        <f t="shared" si="5"/>
+        <v>Analítico de Luz</v>
+      </c>
+      <c r="O33" s="30" t="str">
+        <f t="shared" si="10"/>
+        <v>Ponto.Iluminado</v>
       </c>
       <c r="P33" s="30" t="s">
-        <v>290</v>
+        <v>189</v>
       </c>
       <c r="Q33" s="30" t="s">
-        <v>291</v>
+        <v>191</v>
       </c>
       <c r="R33" s="30" t="s">
-        <v>292</v>
+        <v>195</v>
       </c>
       <c r="S33" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="T33" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>De API</v>
-      </c>
-      <c r="U33" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>Macros</v>
-      </c>
-      <c r="V33" s="66" t="str">
-        <f t="shared" si="21"/>
-        <v>Métodos</v>
+      <c r="T33" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="U33" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="V33" s="30" t="s">
+        <v>234</v>
       </c>
       <c r="W33" s="30" t="s">
         <v>237</v>
       </c>
       <c r="X33" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-33</v>
       </c>
       <c r="Y33" s="67" t="s">
@@ -5709,26 +5849,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="56">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C34" s="62" t="s">
-        <v>278</v>
-      </c>
-      <c r="D34" s="62" t="s">
-        <v>280</v>
-      </c>
-      <c r="E34" s="62" t="s">
-        <v>279</v>
+        <v>262</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E34" s="43" t="s">
+        <v>234</v>
       </c>
       <c r="F34" s="62" t="s">
-        <v>293</v>
-      </c>
-      <c r="G34" s="57" t="s">
+        <v>187</v>
+      </c>
+      <c r="G34" s="63" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="57" t="s">
@@ -5744,50 +5884,47 @@
         <v>9</v>
       </c>
       <c r="L34" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>De API</v>
+        <f t="shared" si="3"/>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M34" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Macros</v>
+        <f t="shared" si="4"/>
+        <v>Elemento.Iluminação</v>
       </c>
       <c r="N34" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O34" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Função Filtro</v>
+        <f t="shared" si="5"/>
+        <v>Analítico de Luz</v>
+      </c>
+      <c r="O34" s="30" t="str">
+        <f t="shared" si="10"/>
+        <v>Linha.Iluminada</v>
       </c>
       <c r="P34" s="30" t="s">
-        <v>294</v>
+        <v>193</v>
       </c>
       <c r="Q34" s="30" t="s">
-        <v>295</v>
+        <v>192</v>
       </c>
       <c r="R34" s="30" t="s">
-        <v>296</v>
+        <v>196</v>
       </c>
       <c r="S34" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="T34" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>De API</v>
-      </c>
-      <c r="U34" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>Macros</v>
-      </c>
-      <c r="V34" s="66" t="str">
-        <f t="shared" si="21"/>
-        <v>Métodos</v>
+      <c r="T34" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="U34" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="V34" s="30" t="s">
+        <v>234</v>
       </c>
       <c r="W34" s="30" t="s">
         <v>237</v>
       </c>
       <c r="X34" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-34</v>
       </c>
       <c r="Y34" s="67" t="s">
@@ -5809,26 +5946,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="56">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C35" s="62" t="s">
-        <v>278</v>
-      </c>
-      <c r="D35" s="62" t="s">
-        <v>280</v>
-      </c>
-      <c r="E35" s="62" t="s">
-        <v>297</v>
+        <v>262</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>234</v>
       </c>
       <c r="F35" s="62" t="s">
-        <v>298</v>
-      </c>
-      <c r="G35" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="G35" s="63" t="s">
         <v>9</v>
       </c>
       <c r="H35" s="57" t="s">
@@ -5844,50 +5981,47 @@
         <v>9</v>
       </c>
       <c r="L35" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>De API</v>
+        <f t="shared" si="3"/>
+        <v>LuminoTécnicos</v>
       </c>
       <c r="M35" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Macros</v>
+        <f t="shared" si="4"/>
+        <v>Elemento.Iluminação</v>
       </c>
       <c r="N35" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O35" s="34" t="str">
-        <f t="shared" si="20"/>
-        <v>Bloco de Código</v>
+        <f t="shared" si="5"/>
+        <v>Analítico de Luz</v>
+      </c>
+      <c r="O35" s="30" t="str">
+        <f t="shared" si="10"/>
+        <v>Area.Iluminada</v>
       </c>
       <c r="P35" s="30" t="s">
-        <v>299</v>
+        <v>190</v>
       </c>
       <c r="Q35" s="30" t="s">
-        <v>300</v>
+        <v>194</v>
       </c>
       <c r="R35" s="30" t="s">
-        <v>301</v>
+        <v>197</v>
       </c>
       <c r="S35" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="T35" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>De API</v>
-      </c>
-      <c r="U35" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>Macros</v>
-      </c>
-      <c r="V35" s="66" t="str">
-        <f t="shared" si="21"/>
-        <v>Códigos Visuais</v>
+      <c r="T35" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="U35" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="V35" s="30" t="s">
+        <v>234</v>
       </c>
       <c r="W35" s="30" t="s">
         <v>237</v>
       </c>
       <c r="X35" s="58" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>Key-ILUM-35</v>
       </c>
       <c r="Y35" s="67" t="s">
@@ -5909,58 +6043,565 @@
         <v>9</v>
       </c>
     </row>
+    <row r="36" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="56">
+        <v>36</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C36" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="D36" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="E36" s="62" t="s">
+        <v>279</v>
+      </c>
+      <c r="F36" s="62" t="s">
+        <v>281</v>
+      </c>
+      <c r="G36" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I36" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J36" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K36" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L36" s="34" t="str">
+        <f t="shared" ref="L36:O40" si="23">SUBSTITUTE(CONCATENATE("", C36), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M36" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Macros</v>
+      </c>
+      <c r="N36" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O36" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P36" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q36" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="R36" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="S36" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T36" s="30" t="str">
+        <f t="shared" ref="T36:V40" si="24">SUBSTITUTE(C36, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U36" s="30" t="str">
+        <f t="shared" si="24"/>
+        <v>Macros</v>
+      </c>
+      <c r="V36" s="66" t="str">
+        <f t="shared" si="24"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W36" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X36" s="58" t="str">
+        <f t="shared" si="9"/>
+        <v>Key-ILUM-36</v>
+      </c>
+      <c r="Y36" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z36" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA36" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB36" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC36" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD36" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="56">
+        <v>37</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C37" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="D37" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="E37" s="62" t="s">
+        <v>279</v>
+      </c>
+      <c r="F37" s="62" t="s">
+        <v>285</v>
+      </c>
+      <c r="G37" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I37" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J37" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K37" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L37" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>De API</v>
+      </c>
+      <c r="M37" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Macros</v>
+      </c>
+      <c r="N37" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O37" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P37" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q37" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="R37" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="S37" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T37" s="30" t="str">
+        <f t="shared" si="24"/>
+        <v>De API</v>
+      </c>
+      <c r="U37" s="30" t="str">
+        <f t="shared" si="24"/>
+        <v>Macros</v>
+      </c>
+      <c r="V37" s="66" t="str">
+        <f t="shared" si="24"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W37" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X37" s="58" t="str">
+        <f t="shared" si="9"/>
+        <v>Key-ILUM-37</v>
+      </c>
+      <c r="Y37" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z37" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA37" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB37" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC37" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD37" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="56">
+        <v>38</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C38" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="D38" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="E38" s="62" t="s">
+        <v>279</v>
+      </c>
+      <c r="F38" s="62" t="s">
+        <v>289</v>
+      </c>
+      <c r="G38" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I38" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J38" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K38" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L38" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>De API</v>
+      </c>
+      <c r="M38" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Macros</v>
+      </c>
+      <c r="N38" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O38" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P38" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q38" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="R38" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="S38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T38" s="30" t="str">
+        <f t="shared" si="24"/>
+        <v>De API</v>
+      </c>
+      <c r="U38" s="30" t="str">
+        <f t="shared" si="24"/>
+        <v>Macros</v>
+      </c>
+      <c r="V38" s="66" t="str">
+        <f t="shared" si="24"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W38" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X38" s="58" t="str">
+        <f t="shared" si="9"/>
+        <v>Key-ILUM-38</v>
+      </c>
+      <c r="Y38" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z38" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA38" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB38" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC38" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD38" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="56">
+        <v>39</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C39" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="D39" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="E39" s="62" t="s">
+        <v>279</v>
+      </c>
+      <c r="F39" s="62" t="s">
+        <v>293</v>
+      </c>
+      <c r="G39" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J39" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K39" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L39" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>De API</v>
+      </c>
+      <c r="M39" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Macros</v>
+      </c>
+      <c r="N39" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O39" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P39" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q39" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="R39" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="S39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T39" s="30" t="str">
+        <f t="shared" si="24"/>
+        <v>De API</v>
+      </c>
+      <c r="U39" s="30" t="str">
+        <f t="shared" si="24"/>
+        <v>Macros</v>
+      </c>
+      <c r="V39" s="66" t="str">
+        <f t="shared" si="24"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W39" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X39" s="58" t="str">
+        <f t="shared" si="9"/>
+        <v>Key-ILUM-39</v>
+      </c>
+      <c r="Y39" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z39" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA39" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB39" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC39" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD39" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="56">
+        <v>40</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C40" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="D40" s="62" t="s">
+        <v>280</v>
+      </c>
+      <c r="E40" s="62" t="s">
+        <v>297</v>
+      </c>
+      <c r="F40" s="62" t="s">
+        <v>298</v>
+      </c>
+      <c r="G40" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I40" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J40" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K40" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L40" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>De API</v>
+      </c>
+      <c r="M40" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Macros</v>
+      </c>
+      <c r="N40" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O40" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P40" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q40" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="R40" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="S40" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T40" s="30" t="str">
+        <f t="shared" si="24"/>
+        <v>De API</v>
+      </c>
+      <c r="U40" s="30" t="str">
+        <f t="shared" si="24"/>
+        <v>Macros</v>
+      </c>
+      <c r="V40" s="66" t="str">
+        <f t="shared" si="24"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W40" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="X40" s="58" t="str">
+        <f t="shared" si="9"/>
+        <v>Key-ILUM-40</v>
+      </c>
+      <c r="Y40" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z40" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA40" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB40" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC40" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD40" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC924">
-    <sortCondition ref="F2:F924"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:AC929">
+    <sortCondition ref="F7:F929"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B35">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+  <conditionalFormatting sqref="A1:O1 R1:Y1 AC1:AD1 R9:R35">
+    <cfRule type="cellIs" dxfId="27" priority="69" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:O1 R1:Y1 AC1:AD1 R4:R30">
-    <cfRule type="cellIs" dxfId="21" priority="63" operator="equal">
+  <conditionalFormatting sqref="E40:F40">
+    <cfRule type="duplicateValues" dxfId="26" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="25" priority="1505"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F8">
+    <cfRule type="duplicateValues" dxfId="19" priority="1527"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9:F35 F41:F1048576">
+    <cfRule type="duplicateValues" dxfId="18" priority="1498"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31 F33:F35">
+    <cfRule type="duplicateValues" dxfId="17" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32">
+    <cfRule type="duplicateValues" dxfId="16" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F36:F39">
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F41:F1048576 F9:F30">
+    <cfRule type="duplicateValues" dxfId="14" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1477"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y6 AA2:AA6 AC2:AC6 A2:B40">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E35:F35">
-    <cfRule type="duplicateValues" dxfId="20" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="19" priority="1499"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
-    <cfRule type="duplicateValues" dxfId="18" priority="1521"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F30 F36:F1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="1492"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26 F28:F30">
-    <cfRule type="duplicateValues" dxfId="16" priority="74"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
-    <cfRule type="duplicateValues" dxfId="15" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F36:F1048576 F4:F25">
-    <cfRule type="duplicateValues" dxfId="13" priority="256"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="1471"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y4:Y27">
-    <cfRule type="containsText" dxfId="10" priority="57" operator="containsText" text="null">
-      <formula>NOT(ISERROR(SEARCH("null",Y4)))</formula>
+  <conditionalFormatting sqref="Y9:Y32">
+    <cfRule type="containsText" dxfId="10" priority="63" operator="containsText" text="null">
+      <formula>NOT(ISERROR(SEARCH("null",Y9)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA25">
-    <cfRule type="duplicateValues" dxfId="9" priority="54"/>
-    <cfRule type="containsText" dxfId="8" priority="55" operator="containsText" text="null">
-      <formula>NOT(ISERROR(SEARCH("null",AA25)))</formula>
+  <conditionalFormatting sqref="AA30">
+    <cfRule type="duplicateValues" dxfId="9" priority="60"/>
+    <cfRule type="containsText" dxfId="8" priority="61" operator="containsText" text="null">
+      <formula>NOT(ISERROR(SEARCH("null",AA30)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="7" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="62"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -5973,15 +6614,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -6046,7 +6687,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -6111,7 +6752,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -6194,30 +6835,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="64.85546875" customWidth="1"/>
-    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" customWidth="1"/>
-    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.28515625" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.7109375" customWidth="1"/>
-    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64.84375" customWidth="1"/>
+    <col min="8" max="8" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.53515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.3828125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.3046875" customWidth="1"/>
+    <col min="14" max="14" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.3046875" customWidth="1"/>
+    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.69140625" customWidth="1"/>
+    <col min="18" max="18" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -6276,7 +6917,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -6335,7 +6976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="21">
         <v>3</v>
       </c>
@@ -6394,7 +7035,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21">
         <v>4</v>
       </c>
@@ -6453,7 +7094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="21">
         <v>5</v>
       </c>
@@ -6512,7 +7153,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="21">
         <v>6</v>
       </c>
@@ -6571,7 +7212,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="21">
         <v>7</v>
       </c>
@@ -6630,7 +7271,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="21">
         <v>8</v>
       </c>
@@ -6689,7 +7330,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="21">
         <v>9</v>
       </c>
@@ -6748,7 +7389,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="21">
         <v>10</v>
       </c>
@@ -6807,7 +7448,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="21">
         <v>11</v>
       </c>
@@ -6866,7 +7507,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="21">
         <v>12</v>
       </c>
@@ -6925,7 +7566,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="21">
         <v>13</v>
       </c>
@@ -6984,7 +7625,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="21">
         <v>14</v>
       </c>
@@ -7053,15 +7694,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="27" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="27" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -7084,7 +7725,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
